--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868162CD-7A2F-4CE7-A363-617ECF84F033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190D2CB6-15AE-4CC5-8C77-7510D0E3D9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="150">
   <si>
     <t>Responsável</t>
   </si>
@@ -67,91 +67,409 @@
     <t>SO/OPM-TS23-BR</t>
   </si>
   <si>
-    <t>DONI- 2803</t>
-  </si>
-  <si>
     <t>Thais Fischer</t>
   </si>
   <si>
-    <t>LP-007615-00-03</t>
-  </si>
-  <si>
-    <t>Body - Retrabalhar dispositivo</t>
-  </si>
-  <si>
-    <t>GILSON</t>
-  </si>
-  <si>
-    <t>PS-AB/ENG1-LA</t>
-  </si>
-  <si>
-    <t>LP-060035</t>
-  </si>
-  <si>
-    <t>4710100392-06</t>
-  </si>
-  <si>
-    <t>Pinça pré brunidora 8mm - pos. 6</t>
-  </si>
-  <si>
     <t>SIU5CT</t>
   </si>
   <si>
-    <t>LP-060037</t>
-  </si>
-  <si>
-    <t>4710100392-07</t>
-  </si>
-  <si>
-    <t>Pinça pré brunidora 8mm - pos. 7</t>
-  </si>
-  <si>
-    <t>LP-060038</t>
-  </si>
-  <si>
-    <t>I68500076283</t>
-  </si>
-  <si>
-    <t>N.A</t>
-  </si>
-  <si>
-    <t>UP CRS - FABRICAÇÃO ELETRODOS ECM</t>
-  </si>
-  <si>
-    <t>ARV2CT</t>
-  </si>
-  <si>
-    <t>LP-060039</t>
-  </si>
-  <si>
-    <t>Adaptador - Fabricação</t>
-  </si>
-  <si>
-    <t>LP-060040</t>
-  </si>
-  <si>
-    <t>Rafael Lima</t>
-  </si>
-  <si>
-    <t>DISPOSITIVO 3D - TAGID TEMPORÁRIA</t>
-  </si>
-  <si>
-    <t>NATEL GUILHE</t>
-  </si>
-  <si>
-    <t>CtP/MFE12</t>
-  </si>
-  <si>
-    <t>LP-060042</t>
-  </si>
-  <si>
-    <t>S/N</t>
-  </si>
-  <si>
-    <t>DU 685438 Parafuso ESPECIAL M5 X 6</t>
-  </si>
-  <si>
-    <t>LP-060043</t>
+    <t>BM-00108513_008_00000014</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Retrabalho do furo de 25 cm</t>
+  </si>
+  <si>
+    <t>ROB2CT</t>
+  </si>
+  <si>
+    <t>PS-DC/ENS1-LA</t>
+  </si>
+  <si>
+    <t>LP-060044</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>685421</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>4716506412-0158</t>
+  </si>
+  <si>
+    <t>LY - conserto</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-060046</t>
+  </si>
+  <si>
+    <t>685411</t>
+  </si>
+  <si>
+    <t>4316502493-0004</t>
+  </si>
+  <si>
+    <t>LP-060047</t>
+  </si>
+  <si>
+    <t>4716400356-0321</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>LP-060048</t>
+  </si>
+  <si>
+    <t>4716400356-0330</t>
+  </si>
+  <si>
+    <t>LP-060049</t>
+  </si>
+  <si>
+    <t>4716403503-0061</t>
+  </si>
+  <si>
+    <t>LP-060050</t>
+  </si>
+  <si>
+    <t>685435</t>
+  </si>
+  <si>
+    <t>4716400512-0098</t>
+  </si>
+  <si>
+    <t>LP-060051</t>
+  </si>
+  <si>
+    <t>4716406271-0001</t>
+  </si>
+  <si>
+    <t>LP-060052</t>
+  </si>
+  <si>
+    <t>4716406272-0001</t>
+  </si>
+  <si>
+    <t>LP-060053</t>
+  </si>
+  <si>
+    <t>685433</t>
+  </si>
+  <si>
+    <t>4712406021</t>
+  </si>
+  <si>
+    <t>Novo - serie 0346</t>
+  </si>
+  <si>
+    <t>LP-060054</t>
+  </si>
+  <si>
+    <t>685434</t>
+  </si>
+  <si>
+    <t>4716506422-0032</t>
+  </si>
+  <si>
+    <t>LP-060055</t>
+  </si>
+  <si>
+    <t>4716507911-0003</t>
+  </si>
+  <si>
+    <t>LP-060056</t>
+  </si>
+  <si>
+    <t>4716507911-0011</t>
+  </si>
+  <si>
+    <t>LP-060057</t>
+  </si>
+  <si>
+    <t>4716507911-0012</t>
+  </si>
+  <si>
+    <t>LP-060058</t>
+  </si>
+  <si>
+    <t>685412</t>
+  </si>
+  <si>
+    <t>4716507911-0013</t>
+  </si>
+  <si>
+    <t>LP-060059</t>
+  </si>
+  <si>
+    <t>4716507911-0015</t>
+  </si>
+  <si>
+    <t>LP-060060</t>
+  </si>
+  <si>
+    <t>4716507911-0019</t>
+  </si>
+  <si>
+    <t>LP-060061</t>
+  </si>
+  <si>
+    <t>4716507911-0021</t>
+  </si>
+  <si>
+    <t>LP-060062</t>
+  </si>
+  <si>
+    <t>4716507911-0022</t>
+  </si>
+  <si>
+    <t>LP-060063</t>
+  </si>
+  <si>
+    <t>4716507911-0025</t>
+  </si>
+  <si>
+    <t>LP-060064</t>
+  </si>
+  <si>
+    <t>4716507911-0026</t>
+  </si>
+  <si>
+    <t>LP-060065</t>
+  </si>
+  <si>
+    <t>4716506419-0044</t>
+  </si>
+  <si>
+    <t>Conex - conserto</t>
+  </si>
+  <si>
+    <t>LP-060066</t>
+  </si>
+  <si>
+    <t>4716507930-0025</t>
+  </si>
+  <si>
+    <t>LP-060067</t>
+  </si>
+  <si>
+    <t>4716507912-0014</t>
+  </si>
+  <si>
+    <t>LP-060068</t>
+  </si>
+  <si>
+    <t>4716507912-0015</t>
+  </si>
+  <si>
+    <t>LP-060069</t>
+  </si>
+  <si>
+    <t>4716507912-0023</t>
+  </si>
+  <si>
+    <t>LP-060070</t>
+  </si>
+  <si>
+    <t>4716507912-0019</t>
+  </si>
+  <si>
+    <t>LP-060071</t>
+  </si>
+  <si>
+    <t>4716507912-0007</t>
+  </si>
+  <si>
+    <t>LP-060072</t>
+  </si>
+  <si>
+    <t>4716507912-0020</t>
+  </si>
+  <si>
+    <t>LP-060073</t>
+  </si>
+  <si>
+    <t>4716507912-0021</t>
+  </si>
+  <si>
+    <t>LP-060074</t>
+  </si>
+  <si>
+    <t>4716507912-0006</t>
+  </si>
+  <si>
+    <t>LP-060075</t>
+  </si>
+  <si>
+    <t>4716507912-0003</t>
+  </si>
+  <si>
+    <t>LP-060076</t>
+  </si>
+  <si>
+    <t>4716507912-0011</t>
+  </si>
+  <si>
+    <t>LP-060077</t>
+  </si>
+  <si>
+    <t>4716507912-0001</t>
+  </si>
+  <si>
+    <t>LP-060078</t>
+  </si>
+  <si>
+    <t>4716406502-0002</t>
+  </si>
+  <si>
+    <t>LP-060079</t>
+  </si>
+  <si>
+    <t>685401</t>
+  </si>
+  <si>
+    <t>4716507090-0010</t>
+  </si>
+  <si>
+    <t>LP-060080</t>
+  </si>
+  <si>
+    <t>4716400379-0012</t>
+  </si>
+  <si>
+    <t>LP-060081</t>
+  </si>
+  <si>
+    <t>4716406422</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 posição 22 e uma posição 216</t>
+  </si>
+  <si>
+    <t>LP-060085</t>
+  </si>
+  <si>
+    <t>685616</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>CHAVE MICRO REBOLO</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>LP-060087</t>
+  </si>
+  <si>
+    <t>N/A'</t>
+  </si>
+  <si>
+    <t>LP-060088</t>
+  </si>
+  <si>
+    <t>685070</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>4719236552</t>
+  </si>
+  <si>
+    <t>Retrabalho Rebolo</t>
+  </si>
+  <si>
+    <t>LP-060091</t>
+  </si>
+  <si>
+    <t>685615</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CONFECÇÃO DISPOSITIVO CRIN BH 23403</t>
+  </si>
+  <si>
+    <t>HENRIQUE O.</t>
+  </si>
+  <si>
+    <t>CtP/MFE31</t>
+  </si>
+  <si>
+    <t>LP-060092</t>
+  </si>
+  <si>
+    <t>685664</t>
+  </si>
+  <si>
+    <t>4729112121</t>
+  </si>
+  <si>
+    <t>FABRICAR FLANGE PARA REBOLO BRUNIM.</t>
+  </si>
+  <si>
+    <t>SOG5CT</t>
+  </si>
+  <si>
+    <t>LP-060094</t>
+  </si>
+  <si>
+    <t>685552</t>
+  </si>
+  <si>
+    <t>4728701187</t>
+  </si>
+  <si>
+    <t>Disco de arraste</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>LP-060095</t>
+  </si>
+  <si>
+    <t>685867</t>
+  </si>
+  <si>
+    <t>4731500499</t>
+  </si>
+  <si>
+    <t>PINO PARA TRAVA</t>
+  </si>
+  <si>
+    <t>ANA LUZ</t>
+  </si>
+  <si>
+    <t>LP-060096</t>
+  </si>
+  <si>
+    <t>4731500506</t>
+  </si>
+  <si>
+    <t>LP-060097</t>
   </si>
 </sst>
 </file>
@@ -514,16 +832,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -567,220 +885,1474 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
-        <v>3</v>
+      <c r="C2" t="s">
+        <v>18</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>685070</v>
-      </c>
-      <c r="C3">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I3">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
-        <v>685070</v>
-      </c>
-      <c r="C4">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I4">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I6">
         <v>500</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
         <v>36</v>
       </c>
-      <c r="B7">
-        <v>685705</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>4725800227</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I7">
-        <v>315</v>
+        <v>500</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>685438</v>
-      </c>
-      <c r="C8">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I8">
         <v>500</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10">
+        <v>500</v>
+      </c>
+      <c r="J10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11">
+        <v>4000</v>
+      </c>
+      <c r="J11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <v>400</v>
+      </c>
+      <c r="J12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13">
+        <v>600</v>
+      </c>
+      <c r="J13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14">
+        <v>600</v>
+      </c>
+      <c r="J14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15">
+        <v>600</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16">
+        <v>600</v>
+      </c>
+      <c r="J16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17">
+        <v>600</v>
+      </c>
+      <c r="J17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18">
+        <v>600</v>
+      </c>
+      <c r="J18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19">
+        <v>600</v>
+      </c>
+      <c r="J19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20">
+        <v>600</v>
+      </c>
+      <c r="J20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21">
+        <v>600</v>
+      </c>
+      <c r="J21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22">
+        <v>600</v>
+      </c>
+      <c r="J22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23">
+        <v>400</v>
+      </c>
+      <c r="J23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24">
+        <v>400</v>
+      </c>
+      <c r="J24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25">
+        <v>600</v>
+      </c>
+      <c r="J25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26">
+        <v>600</v>
+      </c>
+      <c r="J26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27">
+        <v>600</v>
+      </c>
+      <c r="J27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28">
+        <v>600</v>
+      </c>
+      <c r="J28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29">
+        <v>600</v>
+      </c>
+      <c r="J29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30">
+        <v>600</v>
+      </c>
+      <c r="J30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31">
+        <v>600</v>
+      </c>
+      <c r="J31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32">
+        <v>600</v>
+      </c>
+      <c r="J32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33">
+        <v>600</v>
+      </c>
+      <c r="J33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34">
+        <v>600</v>
+      </c>
+      <c r="J34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35">
+        <v>600</v>
+      </c>
+      <c r="J35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36">
+        <v>500</v>
+      </c>
+      <c r="J36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37">
+        <v>500</v>
+      </c>
+      <c r="J37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38">
+        <v>400</v>
+      </c>
+      <c r="J38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" t="s">
+        <v>118</v>
+      </c>
+      <c r="H40" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>120</v>
+      </c>
+      <c r="F41" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" t="s">
+        <v>118</v>
+      </c>
+      <c r="H41" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41">
+        <v>1000</v>
+      </c>
+      <c r="J41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" t="s">
+        <v>125</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42">
+        <v>3000</v>
+      </c>
+      <c r="J42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G43" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" t="s">
+        <v>131</v>
+      </c>
+      <c r="I43">
+        <v>2000</v>
+      </c>
+      <c r="J43" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>134</v>
+      </c>
+      <c r="F44" t="s">
+        <v>135</v>
+      </c>
+      <c r="G44" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44">
+        <v>9000</v>
+      </c>
+      <c r="J44" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>115</v>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>139</v>
+      </c>
+      <c r="F45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45" t="s">
+        <v>141</v>
+      </c>
+      <c r="H45" t="s">
+        <v>12</v>
+      </c>
+      <c r="I45">
+        <v>7040</v>
+      </c>
+      <c r="J45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F46" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" t="s">
+        <v>146</v>
+      </c>
+      <c r="H46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46">
+        <v>1200</v>
+      </c>
+      <c r="J46" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>148</v>
+      </c>
+      <c r="F47" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" t="s">
+        <v>146</v>
+      </c>
+      <c r="H47" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47">
+        <v>1200</v>
+      </c>
+      <c r="J47" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190D2CB6-15AE-4CC5-8C77-7510D0E3D9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F3DAD1-C9CA-481A-A7C9-C28BDCC48CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="151">
   <si>
     <t>Responsável</t>
   </si>
@@ -470,6 +470,9 @@
   </si>
   <si>
     <t>LP-060097</t>
+  </si>
+  <si>
+    <t>Cadastrado</t>
   </si>
 </sst>
 </file>
@@ -845,7 +848,7 @@
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -914,6 +917,9 @@
       <c r="J2" t="s">
         <v>23</v>
       </c>
+      <c r="K2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -946,6 +952,9 @@
       <c r="J3" t="s">
         <v>31</v>
       </c>
+      <c r="K3" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -978,6 +987,9 @@
       <c r="J4" t="s">
         <v>34</v>
       </c>
+      <c r="K4" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1010,6 +1022,9 @@
       <c r="J5" t="s">
         <v>37</v>
       </c>
+      <c r="K5" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1042,6 +1057,9 @@
       <c r="J6" t="s">
         <v>39</v>
       </c>
+      <c r="K6" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1074,6 +1092,9 @@
       <c r="J7" t="s">
         <v>41</v>
       </c>
+      <c r="K7" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1106,6 +1127,9 @@
       <c r="J8" t="s">
         <v>44</v>
       </c>
+      <c r="K8" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1138,6 +1162,9 @@
       <c r="J9" t="s">
         <v>46</v>
       </c>
+      <c r="K9" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1170,6 +1197,9 @@
       <c r="J10" t="s">
         <v>48</v>
       </c>
+      <c r="K10" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1202,6 +1232,9 @@
       <c r="J11" t="s">
         <v>52</v>
       </c>
+      <c r="K11" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1234,6 +1267,9 @@
       <c r="J12" t="s">
         <v>55</v>
       </c>
+      <c r="K12" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1266,6 +1302,9 @@
       <c r="J13" t="s">
         <v>57</v>
       </c>
+      <c r="K13" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1298,6 +1337,9 @@
       <c r="J14" t="s">
         <v>59</v>
       </c>
+      <c r="K14" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1330,6 +1372,9 @@
       <c r="J15" t="s">
         <v>61</v>
       </c>
+      <c r="K15" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1362,8 +1407,11 @@
       <c r="J16" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1394,8 +1442,11 @@
       <c r="J17" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1426,8 +1477,11 @@
       <c r="J18" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1458,8 +1512,11 @@
       <c r="J19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1490,8 +1547,11 @@
       <c r="J20" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1522,8 +1582,11 @@
       <c r="J21" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1554,8 +1617,11 @@
       <c r="J22" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1586,8 +1652,11 @@
       <c r="J23" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1618,8 +1687,11 @@
       <c r="J24" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1650,8 +1722,11 @@
       <c r="J25" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1682,8 +1757,11 @@
       <c r="J26" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -1714,8 +1792,11 @@
       <c r="J27" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -1746,8 +1827,11 @@
       <c r="J28" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -1778,8 +1862,11 @@
       <c r="J29" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -1810,8 +1897,11 @@
       <c r="J30" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1842,8 +1932,11 @@
       <c r="J31" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -1874,8 +1967,11 @@
       <c r="J32" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1906,8 +2002,11 @@
       <c r="J33" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -1938,8 +2037,11 @@
       <c r="J34" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -1970,8 +2072,11 @@
       <c r="J35" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -2002,8 +2107,11 @@
       <c r="J36" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -2034,8 +2142,11 @@
       <c r="J37" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -2066,8 +2177,11 @@
       <c r="J38" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -2098,8 +2212,11 @@
       <c r="J39" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -2130,8 +2247,11 @@
       <c r="J40" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -2162,8 +2282,11 @@
       <c r="J41" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -2194,8 +2317,11 @@
       <c r="J42" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2226,8 +2352,11 @@
       <c r="J43" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K43" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -2258,8 +2387,11 @@
       <c r="J44" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -2290,8 +2422,11 @@
       <c r="J45" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2322,8 +2457,11 @@
       <c r="J46" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2353,6 +2491,9 @@
       </c>
       <c r="J47" t="s">
         <v>149</v>
+      </c>
+      <c r="K47" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33F0484-2FE6-4B2E-84FA-54D84EC74E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB964B28-2400-4854-82C2-99D262AD8E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="173">
   <si>
     <t>Responsável</t>
   </si>
@@ -536,6 +536,9 @@
   </si>
   <si>
     <t>LP-060153</t>
+  </si>
+  <si>
+    <t>Cadastrado</t>
   </si>
 </sst>
 </file>
@@ -911,7 +914,7 @@
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -980,6 +983,9 @@
       <c r="J2" t="s">
         <v>39</v>
       </c>
+      <c r="K2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1012,6 +1018,9 @@
       <c r="J3" t="s">
         <v>43</v>
       </c>
+      <c r="K3" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1044,6 +1053,9 @@
       <c r="J4" t="s">
         <v>46</v>
       </c>
+      <c r="K4" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1076,6 +1088,9 @@
       <c r="J5" t="s">
         <v>50</v>
       </c>
+      <c r="K5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1108,6 +1123,9 @@
       <c r="J6" t="s">
         <v>54</v>
       </c>
+      <c r="K6" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1140,6 +1158,9 @@
       <c r="J7" t="s">
         <v>57</v>
       </c>
+      <c r="K7" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1172,6 +1193,9 @@
       <c r="J8" t="s">
         <v>60</v>
       </c>
+      <c r="K8" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1204,6 +1228,9 @@
       <c r="J9" t="s">
         <v>62</v>
       </c>
+      <c r="K9" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1235,6 +1262,9 @@
       </c>
       <c r="J10" t="s">
         <v>64</v>
+      </c>
+      <c r="K10" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB964B28-2400-4854-82C2-99D262AD8E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8086B33E-8B9F-414F-ACCC-FFCCD590C672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="145">
   <si>
     <t>Responsável</t>
   </si>
@@ -55,462 +55,384 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Thais Fischer</t>
+  </si>
+  <si>
+    <t>Batoques de setup crin</t>
+  </si>
+  <si>
+    <t>ANA LUZ</t>
+  </si>
+  <si>
+    <t>CtP/TEF11</t>
+  </si>
+  <si>
+    <t>LP-060098</t>
+  </si>
+  <si>
+    <t>Cadastrado</t>
+  </si>
+  <si>
     <t>Yesica Gonzalez</t>
   </si>
   <si>
-    <t>CtP/TEF11</t>
+    <t>4711801760</t>
+  </si>
+  <si>
+    <t>Pino</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>LP-060101</t>
+  </si>
+  <si>
+    <t>4729111440</t>
+  </si>
+  <si>
+    <t>Eixo</t>
+  </si>
+  <si>
+    <t>LP-060102</t>
+  </si>
+  <si>
+    <t>4710201043</t>
+  </si>
+  <si>
+    <t>DU 685411 Pino Ø 5mm retificas U.V.A</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>LP-060103</t>
+  </si>
+  <si>
+    <t>4710200283</t>
+  </si>
+  <si>
+    <t>DU 685436 Pino prolongador Bico S</t>
+  </si>
+  <si>
+    <t>LP-060104</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>4716406502</t>
+  </si>
+  <si>
+    <t>Novo - serie 0003</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-060106</t>
+  </si>
+  <si>
+    <t>4716405276</t>
+  </si>
+  <si>
+    <t>Novo - 20un.POS 21 e 01un. POS 22</t>
+  </si>
+  <si>
+    <t>LP-060107</t>
+  </si>
+  <si>
+    <t>4716507926-0014</t>
+  </si>
+  <si>
+    <t>LY - conserto</t>
+  </si>
+  <si>
+    <t>LP-060108</t>
+  </si>
+  <si>
+    <t>4716406393-0001</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>LP-060109</t>
+  </si>
+  <si>
+    <t>4716403503-0003</t>
+  </si>
+  <si>
+    <t>LP-060110</t>
+  </si>
+  <si>
+    <t>4716400356-0322</t>
+  </si>
+  <si>
+    <t>LP-060111</t>
+  </si>
+  <si>
+    <t>4716405933-0023</t>
+  </si>
+  <si>
+    <t>LX - Conserto base</t>
+  </si>
+  <si>
+    <t>LP-060112</t>
+  </si>
+  <si>
+    <t>4316400030-0359</t>
+  </si>
+  <si>
+    <t>LP-060113</t>
+  </si>
+  <si>
+    <t>4716406502-0001</t>
+  </si>
+  <si>
+    <t>LP-060114</t>
+  </si>
+  <si>
+    <t>4716404682-0007</t>
+  </si>
+  <si>
+    <t>LP-060115</t>
+  </si>
+  <si>
+    <t>4716405927-0001</t>
+  </si>
+  <si>
+    <t>LP-060116</t>
+  </si>
+  <si>
+    <t>4716402770-0009</t>
+  </si>
+  <si>
+    <t>LP-060117</t>
+  </si>
+  <si>
+    <t>4716507925-0002</t>
+  </si>
+  <si>
+    <t>LP-060118</t>
+  </si>
+  <si>
+    <t>4710800183</t>
+  </si>
+  <si>
+    <t>IP 685484 Contra Ponto emparelhamento P</t>
+  </si>
+  <si>
+    <t>LP-060120</t>
+  </si>
+  <si>
+    <t>4730500689</t>
+  </si>
+  <si>
+    <t>LP-060121</t>
+  </si>
+  <si>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>4711801456</t>
+  </si>
+  <si>
+    <t>Mandris STH</t>
+  </si>
+  <si>
+    <t>TAT2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-A</t>
+  </si>
+  <si>
+    <t>LP-060122</t>
   </si>
   <si>
     <t>Edson Bento</t>
   </si>
   <si>
+    <t>4729111603</t>
+  </si>
+  <si>
+    <t>POSIÇÃO 001</t>
+  </si>
+  <si>
+    <t>YOI1CT</t>
+  </si>
+  <si>
     <t>SO/OPM-TS23-BR</t>
   </si>
   <si>
-    <t>Thais Fischer</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Rodrigo Melo</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>LY - conserto</t>
-  </si>
-  <si>
-    <t>QMM</t>
-  </si>
-  <si>
-    <t>PS/QMM7-CtP</t>
-  </si>
-  <si>
-    <t>685411</t>
-  </si>
-  <si>
-    <t>LX - Conserto</t>
-  </si>
-  <si>
-    <t>685435</t>
-  </si>
-  <si>
-    <t>685433</t>
-  </si>
-  <si>
-    <t>685412</t>
-  </si>
-  <si>
-    <t>685401</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>685615</t>
+    <t>LP-060123</t>
+  </si>
+  <si>
+    <t>POSIÇÃO 002</t>
+  </si>
+  <si>
+    <t>LP-060124</t>
+  </si>
+  <si>
+    <t>POSIÇÃO 008</t>
+  </si>
+  <si>
+    <t>LP-060125</t>
+  </si>
+  <si>
+    <t>RETRABALHO DISPOSITIVO DOBRADEIRA DHK</t>
+  </si>
+  <si>
+    <t>LP-060127</t>
+  </si>
+  <si>
+    <t>4710101138</t>
+  </si>
+  <si>
+    <t>IP 685485 Pinça garra brunidora CIL P3</t>
+  </si>
+  <si>
+    <t>LP-060128</t>
+  </si>
+  <si>
+    <t>4710800351</t>
+  </si>
+  <si>
+    <t>Contra ponto</t>
+  </si>
+  <si>
+    <t>LP-060129</t>
+  </si>
+  <si>
+    <t>4304.800.262</t>
+  </si>
+  <si>
+    <t>IP 685484 Rebolo borazon Pistão A/P</t>
+  </si>
+  <si>
+    <t>LP-060130</t>
+  </si>
+  <si>
+    <t>4304.800.229</t>
+  </si>
+  <si>
+    <t>LP-060131</t>
+  </si>
+  <si>
+    <t>4719.266.003</t>
+  </si>
+  <si>
+    <t>LP-060132</t>
+  </si>
+  <si>
+    <t>4719.266.007</t>
+  </si>
+  <si>
+    <t>LP-060133</t>
+  </si>
+  <si>
+    <t>4304800434</t>
+  </si>
+  <si>
+    <t>LP-060134</t>
+  </si>
+  <si>
+    <t>4304800433</t>
+  </si>
+  <si>
+    <t>DONI- 2803D</t>
+  </si>
+  <si>
+    <t>LP-060135</t>
+  </si>
+  <si>
+    <t>4719266046</t>
+  </si>
+  <si>
+    <t>LP-060136</t>
+  </si>
+  <si>
+    <t>4710101560</t>
+  </si>
+  <si>
+    <t>IP 685485 Pinça CIL P ⌀12 Zema 4593</t>
+  </si>
+  <si>
+    <t>LP-060137</t>
+  </si>
+  <si>
+    <t>4719266051</t>
+  </si>
+  <si>
+    <t>LP-060138</t>
+  </si>
+  <si>
+    <t>4718300305</t>
+  </si>
+  <si>
+    <t>IP 685487  Apalpador retifica fortuna</t>
+  </si>
+  <si>
+    <t>LP-060139</t>
+  </si>
+  <si>
+    <t>4729104510</t>
+  </si>
+  <si>
+    <t>Disp. Nagel</t>
+  </si>
+  <si>
+    <t>LP-060140</t>
+  </si>
+  <si>
+    <t>4710101504</t>
+  </si>
+  <si>
+    <t>IP 685486 Pinça ∅11 Zema 4593 EL H</t>
+  </si>
+  <si>
+    <t>LP-060141</t>
+  </si>
+  <si>
+    <t>4729110620</t>
+  </si>
+  <si>
+    <t>IP 685487 Vareta de presença Brunidoras.</t>
+  </si>
+  <si>
+    <t>LP-060142</t>
+  </si>
+  <si>
+    <t>Novo modelo das tags STH</t>
+  </si>
+  <si>
+    <t>MMA5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-B</t>
+  </si>
+  <si>
+    <t>LP-060148</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>Revisão placa UVA CRIN</t>
+  </si>
+  <si>
     <t>HENRIQUE O.</t>
   </si>
   <si>
     <t>CtP/MFE31</t>
   </si>
   <si>
-    <t>DOUGLAS</t>
-  </si>
-  <si>
-    <t>ANA LUZ</t>
-  </si>
-  <si>
-    <t>685608</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Batoques de setup crin</t>
-  </si>
-  <si>
-    <t>LP-060098</t>
-  </si>
-  <si>
-    <t>685551</t>
-  </si>
-  <si>
-    <t>4711801760</t>
-  </si>
-  <si>
-    <t>Pino</t>
-  </si>
-  <si>
-    <t>LP-060101</t>
-  </si>
-  <si>
-    <t>4729111440</t>
-  </si>
-  <si>
-    <t>Eixo</t>
-  </si>
-  <si>
-    <t>LP-060102</t>
-  </si>
-  <si>
-    <t>4710201043</t>
-  </si>
-  <si>
-    <t>DU 685411 Pino Ø 5mm retificas U.V.A</t>
-  </si>
-  <si>
-    <t>DONI- 2803</t>
-  </si>
-  <si>
-    <t>LP-060103</t>
-  </si>
-  <si>
-    <t>685436</t>
-  </si>
-  <si>
-    <t>4710200283</t>
-  </si>
-  <si>
-    <t>DU 685436 Pino prolongador Bico S</t>
-  </si>
-  <si>
-    <t>LP-060104</t>
-  </si>
-  <si>
-    <t>4716406502</t>
-  </si>
-  <si>
-    <t>Novo - serie 0003</t>
-  </si>
-  <si>
-    <t>LP-060106</t>
-  </si>
-  <si>
-    <t>4716405276</t>
-  </si>
-  <si>
-    <t>Novo - 20un.POS 21 e 01un. POS 22</t>
-  </si>
-  <si>
-    <t>LP-060107</t>
-  </si>
-  <si>
-    <t>4716507926-0014</t>
-  </si>
-  <si>
-    <t>LP-060108</t>
-  </si>
-  <si>
-    <t>4716406393-0001</t>
-  </si>
-  <si>
-    <t>LP-060109</t>
-  </si>
-  <si>
-    <t>4716403503-0003</t>
-  </si>
-  <si>
-    <t>LP-060110</t>
-  </si>
-  <si>
-    <t>4716400356-0322</t>
-  </si>
-  <si>
-    <t>LP-060111</t>
-  </si>
-  <si>
-    <t>4716405933-0023</t>
-  </si>
-  <si>
-    <t>LX - Conserto base</t>
-  </si>
-  <si>
-    <t>LP-060112</t>
-  </si>
-  <si>
-    <t>4316400030-0359</t>
-  </si>
-  <si>
-    <t>LP-060113</t>
-  </si>
-  <si>
-    <t>4716406502-0001</t>
-  </si>
-  <si>
-    <t>LP-060114</t>
-  </si>
-  <si>
-    <t>4716404682-0007</t>
-  </si>
-  <si>
-    <t>LP-060115</t>
-  </si>
-  <si>
-    <t>4716405927-0001</t>
-  </si>
-  <si>
-    <t>LP-060116</t>
-  </si>
-  <si>
-    <t>4716402770-0009</t>
-  </si>
-  <si>
-    <t>LP-060117</t>
-  </si>
-  <si>
-    <t>4716507925-0002</t>
-  </si>
-  <si>
-    <t>LP-060118</t>
-  </si>
-  <si>
-    <t>685484</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>4710800183</t>
-  </si>
-  <si>
-    <t>IP 685484 Contra Ponto emparelhamento P</t>
-  </si>
-  <si>
-    <t>LP-060120</t>
-  </si>
-  <si>
-    <t>685546</t>
-  </si>
-  <si>
-    <t>4730500689</t>
-  </si>
-  <si>
-    <t>LP-060121</t>
-  </si>
-  <si>
-    <t>Marcelo Simoes</t>
-  </si>
-  <si>
-    <t>4711801456</t>
-  </si>
-  <si>
-    <t>Mandris STH</t>
-  </si>
-  <si>
-    <t>TAT2CT</t>
-  </si>
-  <si>
-    <t>CtP/MFW12-A</t>
-  </si>
-  <si>
-    <t>LP-060122</t>
-  </si>
-  <si>
-    <t>685009</t>
-  </si>
-  <si>
-    <t>4729111603</t>
-  </si>
-  <si>
-    <t>POSIÇÃO 001</t>
-  </si>
-  <si>
-    <t>YOI1CT</t>
-  </si>
-  <si>
-    <t>LP-060123</t>
-  </si>
-  <si>
-    <t>POSIÇÃO 002</t>
-  </si>
-  <si>
-    <t>LP-060124</t>
-  </si>
-  <si>
-    <t>POSIÇÃO 008</t>
-  </si>
-  <si>
-    <t>LP-060125</t>
-  </si>
-  <si>
-    <t>RETRABALHO DISPOSITIVO DOBRADEIRA DHK</t>
-  </si>
-  <si>
-    <t>LP-060127</t>
-  </si>
-  <si>
-    <t>685485</t>
-  </si>
-  <si>
-    <t>4710101138</t>
-  </si>
-  <si>
-    <t>IP 685485 Pinça garra brunidora CIL P3</t>
-  </si>
-  <si>
-    <t>LP-060128</t>
-  </si>
-  <si>
-    <t>685008</t>
-  </si>
-  <si>
-    <t>4710800351</t>
-  </si>
-  <si>
-    <t>Contra ponto</t>
-  </si>
-  <si>
-    <t>LP-060129</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>4304.800.262</t>
-  </si>
-  <si>
-    <t>IP 685484 Rebolo borazon Pistão A/P</t>
-  </si>
-  <si>
-    <t>LP-060130</t>
-  </si>
-  <si>
-    <t>4304.800.229</t>
-  </si>
-  <si>
-    <t>LP-060131</t>
-  </si>
-  <si>
-    <t>4719.266.003</t>
-  </si>
-  <si>
-    <t>LP-060132</t>
-  </si>
-  <si>
-    <t>4719.266.007</t>
-  </si>
-  <si>
-    <t>LP-060133</t>
-  </si>
-  <si>
-    <t>4304800434</t>
-  </si>
-  <si>
-    <t>LP-060134</t>
-  </si>
-  <si>
-    <t>4304800433</t>
-  </si>
-  <si>
-    <t>DONI- 2803D</t>
-  </si>
-  <si>
-    <t>LP-060135</t>
-  </si>
-  <si>
-    <t>4719266046</t>
-  </si>
-  <si>
-    <t>LP-060136</t>
-  </si>
-  <si>
-    <t>4710101560</t>
-  </si>
-  <si>
-    <t>IP 685485 Pinça CIL P ⌀12 Zema 4593</t>
-  </si>
-  <si>
-    <t>LP-060137</t>
-  </si>
-  <si>
-    <t>4719266051</t>
-  </si>
-  <si>
-    <t>LP-060138</t>
-  </si>
-  <si>
-    <t>685487</t>
-  </si>
-  <si>
-    <t>4718300305</t>
-  </si>
-  <si>
-    <t>IP 685487  Apalpador retifica fortuna</t>
-  </si>
-  <si>
-    <t>LP-060139</t>
-  </si>
-  <si>
-    <t>685541</t>
-  </si>
-  <si>
-    <t>4729104510</t>
-  </si>
-  <si>
-    <t>Disp. Nagel</t>
-  </si>
-  <si>
-    <t>LP-060140</t>
-  </si>
-  <si>
-    <t>685486</t>
-  </si>
-  <si>
-    <t>4710101504</t>
-  </si>
-  <si>
-    <t>IP 685486 Pinça ∅11 Zema 4593 EL H</t>
-  </si>
-  <si>
-    <t>LP-060141</t>
-  </si>
-  <si>
-    <t>4729110620</t>
-  </si>
-  <si>
-    <t>IP 685487 Vareta de presença Brunidoras.</t>
-  </si>
-  <si>
-    <t>LP-060142</t>
-  </si>
-  <si>
-    <t>685101</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Novo modelo das tags STH</t>
-  </si>
-  <si>
-    <t>MMA5CT</t>
-  </si>
-  <si>
-    <t>CtP/MFW12-B</t>
-  </si>
-  <si>
-    <t>LP-060148</t>
-  </si>
-  <si>
-    <t>Revisão placa UVA CRIN</t>
-  </si>
-  <si>
     <t>LP-060149</t>
   </si>
   <si>
-    <t>685071</t>
-  </si>
-  <si>
     <t>4729102164</t>
   </si>
   <si>
@@ -523,9 +445,6 @@
     <t>LP-060152</t>
   </si>
   <si>
-    <t>685655</t>
-  </si>
-  <si>
     <t>47 291 06 045</t>
   </si>
   <si>
@@ -536,27 +455,19 @@
   </si>
   <si>
     <t>LP-060153</t>
-  </si>
-  <si>
-    <t>Cadastrado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -567,7 +478,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -575,30 +486,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,1473 +811,1572 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>685608</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>28000</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>685551</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
       </c>
       <c r="D3">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>800</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>685401</v>
+      </c>
+      <c r="C4">
+        <v>19</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I4">
         <v>3900</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>685411</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5">
         <v>3960</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K5" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>685436</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>3000</v>
       </c>
       <c r="J6" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>685411</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I7">
         <v>1800</v>
       </c>
       <c r="J7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>685411</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
       </c>
       <c r="D8">
         <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I8">
         <v>6000</v>
       </c>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>685433</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I9">
         <v>400</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>685412</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I10">
         <v>500</v>
       </c>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="K10" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>685411</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I11">
         <v>500</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>48</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B12">
+        <v>685411</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I12">
         <v>500</v>
       </c>
       <c r="J12" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>685411</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I13">
         <v>400</v>
       </c>
       <c r="J13" t="s">
-        <v>71</v>
+        <v>53</v>
+      </c>
+      <c r="K13" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B14">
+        <v>685401</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I14">
         <v>400</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="K14" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>685411</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I15">
         <v>800</v>
       </c>
       <c r="J15" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="K15" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>685435</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I16">
         <v>600</v>
       </c>
       <c r="J16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>685412</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I17">
         <v>600</v>
       </c>
       <c r="J17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="K17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>685401</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I18">
         <v>1500</v>
       </c>
       <c r="J18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="K18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>685433</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I19">
         <v>500</v>
       </c>
       <c r="J19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="K19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>685484</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
       </c>
       <c r="D20">
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I20">
         <v>1320</v>
       </c>
       <c r="J20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="K20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B21">
+        <v>685546</v>
+      </c>
+      <c r="C21">
+        <v>19</v>
       </c>
       <c r="D21">
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I21">
         <v>1760</v>
       </c>
       <c r="J21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>28</v>
+        <v>71</v>
+      </c>
+      <c r="B22">
+        <v>685546</v>
+      </c>
+      <c r="C22">
+        <v>19</v>
       </c>
       <c r="D22">
         <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="I22">
         <v>2500</v>
       </c>
       <c r="J22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="K22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
+        <v>77</v>
+      </c>
+      <c r="B23">
+        <v>685009</v>
+      </c>
+      <c r="C23">
+        <v>19</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I23">
         <v>2500</v>
       </c>
       <c r="J23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="K23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
+        <v>77</v>
+      </c>
+      <c r="B24">
+        <v>685009</v>
+      </c>
+      <c r="C24">
+        <v>19</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I24">
         <v>2000</v>
       </c>
       <c r="J24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="K24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" t="s">
-        <v>28</v>
+        <v>77</v>
+      </c>
+      <c r="B25">
+        <v>685009</v>
+      </c>
+      <c r="C25">
+        <v>19</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I25">
         <v>750</v>
       </c>
       <c r="J25" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="K25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" t="s">
-        <v>28</v>
+        <v>77</v>
+      </c>
+      <c r="B26">
+        <v>685009</v>
+      </c>
+      <c r="C26">
+        <v>19</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I26">
         <v>600</v>
       </c>
       <c r="J26" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="K26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>685485</v>
+      </c>
+      <c r="C27">
+        <v>19</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I27">
         <v>2500</v>
       </c>
       <c r="J27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="K27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>685008</v>
+      </c>
+      <c r="C28">
+        <v>19</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I28">
         <v>500</v>
       </c>
       <c r="J28" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="K28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>685484</v>
+      </c>
+      <c r="C29">
+        <v>37</v>
       </c>
       <c r="D29">
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="F29" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I29">
         <v>880</v>
       </c>
       <c r="J29" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="K29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B30">
+        <v>685484</v>
+      </c>
+      <c r="C30">
+        <v>37</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G30" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I30">
         <v>550</v>
       </c>
       <c r="J30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="K30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B31">
+        <v>685484</v>
+      </c>
+      <c r="C31">
+        <v>37</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I31">
         <v>330</v>
       </c>
       <c r="J31" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="K31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>685484</v>
+      </c>
+      <c r="C32">
+        <v>37</v>
       </c>
       <c r="D32">
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I32">
         <v>330</v>
       </c>
       <c r="J32" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>685484</v>
+      </c>
+      <c r="C33">
+        <v>37</v>
       </c>
       <c r="D33">
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="F33" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I33">
         <v>1100</v>
       </c>
       <c r="J33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="K33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>685484</v>
+      </c>
+      <c r="C34">
+        <v>37</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I34">
         <v>550</v>
       </c>
       <c r="J34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>685484</v>
+      </c>
+      <c r="C35">
+        <v>37</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F35" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H35" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I35">
         <v>550</v>
       </c>
       <c r="J35" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="K35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B36">
+        <v>685485</v>
+      </c>
+      <c r="C36">
+        <v>19</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F36" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="G36" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H36" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I36">
         <v>4400</v>
       </c>
       <c r="J36" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="K36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>117</v>
+        <v>17</v>
+      </c>
+      <c r="B37">
+        <v>685484</v>
+      </c>
+      <c r="C37">
+        <v>37</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G37" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I37">
         <v>110</v>
       </c>
       <c r="J37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" t="s">
-        <v>139</v>
-      </c>
-      <c r="C38" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B38">
+        <v>685487</v>
+      </c>
+      <c r="C38">
+        <v>19</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="E38" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="F38" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="G38" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I38">
         <v>1500</v>
       </c>
       <c r="J38" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B39">
+        <v>685541</v>
+      </c>
+      <c r="C39">
+        <v>19</v>
       </c>
       <c r="D39">
         <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="F39" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="G39" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I39">
         <v>600</v>
       </c>
       <c r="J39" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="K39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B40">
+        <v>685486</v>
+      </c>
+      <c r="C40">
+        <v>19</v>
       </c>
       <c r="D40">
         <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="F40" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="G40" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I40">
         <v>5500</v>
       </c>
       <c r="J40" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="K40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B41">
+        <v>685487</v>
+      </c>
+      <c r="C41">
+        <v>19</v>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H41" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I41">
         <v>2750</v>
       </c>
       <c r="J41" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="K41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" t="s">
-        <v>154</v>
-      </c>
-      <c r="C42" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B42">
+        <v>685101</v>
+      </c>
+      <c r="C42">
+        <v>19</v>
       </c>
       <c r="D42">
         <v>20</v>
       </c>
-      <c r="E42" t="s">
-        <v>155</v>
-      </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="G42" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="H42" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="I42">
         <v>3200</v>
       </c>
       <c r="J42" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="K42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" t="s">
-        <v>28</v>
+        <v>71</v>
+      </c>
+      <c r="B43">
+        <v>685615</v>
+      </c>
+      <c r="C43">
+        <v>19</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="F43" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="H43" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="I43">
         <v>1000</v>
       </c>
       <c r="J43" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>92</v>
-      </c>
-      <c r="B44" t="s">
-        <v>162</v>
-      </c>
-      <c r="C44" t="s">
-        <v>16</v>
+        <v>71</v>
+      </c>
+      <c r="B44">
+        <v>685071</v>
+      </c>
+      <c r="C44">
+        <v>5</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="F44" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I44">
         <v>1000</v>
       </c>
       <c r="J44" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" t="s">
-        <v>167</v>
-      </c>
-      <c r="C45" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B45">
+        <v>685655</v>
+      </c>
+      <c r="C45">
+        <v>19</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="F45" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="G45" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="H45" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I45">
         <v>1650</v>
       </c>
       <c r="J45" t="s">
-        <v>171</v>
+        <v>144</v>
+      </c>
+      <c r="K45" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69057110-2713-4A47-BFB9-7E2C9AA22321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66558FD-7E80-465C-A7C3-BF037CFEC601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="164">
   <si>
     <t>Responsável</t>
   </si>
@@ -64,18 +64,6 @@
     <t>DOUGLAS</t>
   </si>
   <si>
-    <t>Rodrigo Melo</t>
-  </si>
-  <si>
-    <t>QMM</t>
-  </si>
-  <si>
-    <t>PS/QMM7-CtP</t>
-  </si>
-  <si>
-    <t>LX - Conserto</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -85,106 +73,445 @@
     <t>19</t>
   </si>
   <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>685605</t>
-  </si>
-  <si>
-    <t>685608</t>
-  </si>
-  <si>
     <t>Renato Meira</t>
   </si>
   <si>
-    <t>685612</t>
-  </si>
-  <si>
     <t>685616</t>
   </si>
   <si>
-    <t>LO - conserto</t>
-  </si>
-  <si>
-    <t>4715300888-0003</t>
-  </si>
-  <si>
-    <t>LP-060241</t>
-  </si>
-  <si>
-    <t>4716404440-0002</t>
-  </si>
-  <si>
-    <t>LP-060242</t>
-  </si>
-  <si>
-    <t>4714900147</t>
-  </si>
-  <si>
-    <t>Novo - serie 0014</t>
-  </si>
-  <si>
-    <t>LP-060243</t>
-  </si>
-  <si>
-    <t>4738360385-0039</t>
-  </si>
-  <si>
-    <t>OGIVA - conserto</t>
-  </si>
-  <si>
-    <t>LP-060244</t>
-  </si>
-  <si>
-    <t>Desenhos tubetes st180 - pos 32</t>
-  </si>
-  <si>
-    <t>SNA2CT</t>
-  </si>
-  <si>
-    <t>LP-060247</t>
-  </si>
-  <si>
-    <t>685551</t>
-  </si>
-  <si>
-    <t>4711201112</t>
-  </si>
-  <si>
-    <t>Posição 1</t>
-  </si>
-  <si>
-    <t>LP-060248</t>
-  </si>
-  <si>
-    <t>4750005005</t>
-  </si>
-  <si>
-    <t>Bucha  - Posição 2</t>
-  </si>
-  <si>
-    <t>OLE8CT</t>
-  </si>
-  <si>
     <t>CtP/MFE21</t>
   </si>
   <si>
-    <t>LP-060249</t>
-  </si>
-  <si>
-    <t>4729109677</t>
-  </si>
-  <si>
-    <t>LP-060250</t>
-  </si>
-  <si>
-    <t>4729106296</t>
-  </si>
-  <si>
-    <t>LP-060251</t>
-  </si>
-  <si>
-    <t>Cadastrado</t>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>LP-047032</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>3418260604</t>
+  </si>
+  <si>
+    <t>Retificar Arrastador e topo Pistão LE</t>
+  </si>
+  <si>
+    <t>COR4CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE12</t>
+  </si>
+  <si>
+    <t>LP-060252</t>
+  </si>
+  <si>
+    <t>Rafael Lima</t>
+  </si>
+  <si>
+    <t>685907</t>
+  </si>
+  <si>
+    <t>4725800244</t>
+  </si>
+  <si>
+    <t>EXECUTAR IMPRESSÃO 3D</t>
+  </si>
+  <si>
+    <t>SOC2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-A</t>
+  </si>
+  <si>
+    <t>LP-060253</t>
+  </si>
+  <si>
+    <t>685486</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>4729111811</t>
+  </si>
+  <si>
+    <t>DISCO DE ARRASTE ZEMA</t>
+  </si>
+  <si>
+    <t>SIU5CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>LP-060255</t>
+  </si>
+  <si>
+    <t>6855008</t>
+  </si>
+  <si>
+    <t>4729111796</t>
+  </si>
+  <si>
+    <t>Retrabalho dispostivo HPC</t>
+  </si>
+  <si>
+    <t>MMA5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW11-C</t>
+  </si>
+  <si>
+    <t>LP-060256</t>
+  </si>
+  <si>
+    <t>685617</t>
+  </si>
+  <si>
+    <t>4717600141</t>
+  </si>
+  <si>
+    <t>OLH2CT</t>
+  </si>
+  <si>
+    <t>LP-060257</t>
+  </si>
+  <si>
+    <t>4717600101</t>
+  </si>
+  <si>
+    <t>LP-060258</t>
+  </si>
+  <si>
+    <t>4717600132</t>
+  </si>
+  <si>
+    <t>LP-060259</t>
+  </si>
+  <si>
+    <t>BM-00108513_002_00000018</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>N.A</t>
+  </si>
+  <si>
+    <t>FCu retifica</t>
+  </si>
+  <si>
+    <t>FOM2CT</t>
+  </si>
+  <si>
+    <t>CtP/ETS</t>
+  </si>
+  <si>
+    <t>LP-060261</t>
+  </si>
+  <si>
+    <t>685552</t>
+  </si>
+  <si>
+    <t>4710800278</t>
+  </si>
+  <si>
+    <t>685552 - Retrabalho Ponto ZEMA (Valvula)</t>
+  </si>
+  <si>
+    <t>VIM2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE11</t>
+  </si>
+  <si>
+    <t>LP-060262</t>
+  </si>
+  <si>
+    <t>685411</t>
+  </si>
+  <si>
+    <t>4729111452</t>
+  </si>
+  <si>
+    <t>DU 685411 Pino torno benzinger placa nov</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>LP-060263</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>4729105567_POS 1</t>
+  </si>
+  <si>
+    <t>DU 685411 POSIÇÃO 1 da Placa silberhorn</t>
+  </si>
+  <si>
+    <t>LP-060264</t>
+  </si>
+  <si>
+    <t>4710101475</t>
+  </si>
+  <si>
+    <t>DU 685411 Garra d Pinça H.Rebaixada HTT</t>
+  </si>
+  <si>
+    <t>LP-060265</t>
+  </si>
+  <si>
+    <t>4710800193</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto Haste Cheia U.D</t>
+  </si>
+  <si>
+    <t>LP-060266</t>
+  </si>
+  <si>
+    <t>4710800199</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto retífica Bhamulle</t>
+  </si>
+  <si>
+    <t>LP-060267</t>
+  </si>
+  <si>
+    <t>685615</t>
+  </si>
+  <si>
+    <t>4729107091</t>
+  </si>
+  <si>
+    <t>Anel Interno Atmo</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>LP-060268</t>
+  </si>
+  <si>
+    <t>4741420045</t>
+  </si>
+  <si>
+    <t>Ponteira de Medição</t>
+  </si>
+  <si>
+    <t>LP-060269</t>
+  </si>
+  <si>
+    <t>685703</t>
+  </si>
+  <si>
+    <t>4719241071</t>
+  </si>
+  <si>
+    <t>REBOLO LCMV</t>
+  </si>
+  <si>
+    <t>REGIMARA</t>
+  </si>
+  <si>
+    <t>LP-060273</t>
+  </si>
+  <si>
+    <t>685554</t>
+  </si>
+  <si>
+    <t>4702900326</t>
+  </si>
+  <si>
+    <t>PINO DE CONTATO ELETRODO</t>
+  </si>
+  <si>
+    <t>LP-060274</t>
+  </si>
+  <si>
+    <t>4712001839</t>
+  </si>
+  <si>
+    <t>Garra</t>
+  </si>
+  <si>
+    <t>LP-060280</t>
+  </si>
+  <si>
+    <t>685553</t>
+  </si>
+  <si>
+    <t>471090069</t>
+  </si>
+  <si>
+    <t>Ponteira</t>
+  </si>
+  <si>
+    <t>LP-060281</t>
+  </si>
+  <si>
+    <t>4729106006</t>
+  </si>
+  <si>
+    <t>Bujão ZPD</t>
+  </si>
+  <si>
+    <t>LP-060282</t>
+  </si>
+  <si>
+    <t>685664</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>BASE DA CAIXA</t>
+  </si>
+  <si>
+    <t>BRUNO ARAUJO</t>
+  </si>
+  <si>
+    <t>LP-060283</t>
+  </si>
+  <si>
+    <t>TAMPA DA CAIXA</t>
+  </si>
+  <si>
+    <t>LP-060284</t>
+  </si>
+  <si>
+    <t>685622</t>
+  </si>
+  <si>
+    <t>SUPORTE SP</t>
+  </si>
+  <si>
+    <t>TKC1CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS21-BR</t>
+  </si>
+  <si>
+    <t>LP-060289</t>
+  </si>
+  <si>
+    <t>SUPORTE SPS</t>
+  </si>
+  <si>
+    <t>LP-060290</t>
+  </si>
+  <si>
+    <t>685606</t>
+  </si>
+  <si>
+    <t>4729110910</t>
+  </si>
+  <si>
+    <t>Vedação st.120 - pos 02</t>
+  </si>
+  <si>
+    <t>ZAK2CT</t>
+  </si>
+  <si>
+    <t>LP-060293</t>
+  </si>
+  <si>
+    <t>685541</t>
+  </si>
+  <si>
+    <t>4730502020</t>
+  </si>
+  <si>
+    <t>Pino guia</t>
+  </si>
+  <si>
+    <t>LP-060294</t>
+  </si>
+  <si>
+    <t>4711500224</t>
+  </si>
+  <si>
+    <t>DU 685411 Pino HTT 23352 QUEBRADO.</t>
+  </si>
+  <si>
+    <t>LP-060295</t>
+  </si>
+  <si>
+    <t>4728603019</t>
+  </si>
+  <si>
+    <t>Haste st. 10 - pos 04</t>
+  </si>
+  <si>
+    <t>LP-060296</t>
+  </si>
+  <si>
+    <t>4728701153</t>
+  </si>
+  <si>
+    <t>Crin 1/2</t>
+  </si>
+  <si>
+    <t>ANF2CT</t>
+  </si>
+  <si>
+    <t>LP-060299</t>
+  </si>
+  <si>
+    <t>Crin 3</t>
+  </si>
+  <si>
+    <t>LP-060300</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Criação de desenho</t>
+  </si>
+  <si>
+    <t>IAP3CT</t>
+  </si>
+  <si>
+    <t>LP-060315</t>
+  </si>
+  <si>
+    <t>685401</t>
+  </si>
+  <si>
+    <t>4729109899/BB5504</t>
+  </si>
+  <si>
+    <t>Expulsor</t>
+  </si>
+  <si>
+    <t>LP-060316</t>
+  </si>
+  <si>
+    <t>Roda do separador CRIN3 - BH8000</t>
+  </si>
+  <si>
+    <t>HENRIQUE O.</t>
+  </si>
+  <si>
+    <t>LP-060318</t>
+  </si>
+  <si>
+    <t>Criação de norma e desenho batente</t>
+  </si>
+  <si>
+    <t>LP-060319</t>
+  </si>
+  <si>
+    <t>Roda do separador CRIN1/2 - BH8000</t>
+  </si>
+  <si>
+    <t>LP-060320</t>
   </si>
 </sst>
 </file>
@@ -524,20 +851,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -577,317 +904,1154 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
       <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2">
+        <v>5000</v>
+      </c>
+      <c r="J2" t="s">
         <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2">
-        <v>4000</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I4">
-        <v>4000</v>
+        <v>720</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>1440</v>
+        <v>12000</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>10</v>
-      </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="I8">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I9">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10">
+        <v>300</v>
+      </c>
+      <c r="J10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11">
+        <v>3400</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12">
+        <v>1100</v>
+      </c>
+      <c r="J12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>4720</v>
+      </c>
+      <c r="J13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14">
+        <v>4400</v>
+      </c>
+      <c r="J14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15">
+        <v>2640</v>
+      </c>
+      <c r="J15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16">
+        <v>2500</v>
+      </c>
+      <c r="J16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17">
+        <v>1020</v>
+      </c>
+      <c r="J17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>200</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18">
+        <v>1760</v>
+      </c>
+      <c r="J18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19">
+        <v>13800</v>
+      </c>
+      <c r="J19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20">
+        <v>4000</v>
+      </c>
+      <c r="J20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21">
+        <v>1500</v>
+      </c>
+      <c r="J21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22">
         <v>20</v>
       </c>
-      <c r="D10">
+      <c r="E22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22">
+        <v>3300</v>
+      </c>
+      <c r="J22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23">
+        <v>230</v>
+      </c>
+      <c r="J23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24">
+        <v>445</v>
+      </c>
+      <c r="J24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" t="s">
+        <v>123</v>
+      </c>
+      <c r="H25" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25">
+        <v>225</v>
+      </c>
+      <c r="J25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26">
+        <v>180</v>
+      </c>
+      <c r="J26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27">
         <v>10</v>
       </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10">
-        <v>5000</v>
-      </c>
-      <c r="J10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" t="s">
-        <v>54</v>
+      <c r="E27" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27">
+        <v>1100</v>
+      </c>
+      <c r="J27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28">
+        <v>1120</v>
+      </c>
+      <c r="J28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" t="s">
+        <v>131</v>
+      </c>
+      <c r="H30" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30">
+        <v>4300</v>
+      </c>
+      <c r="J30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31">
+        <v>1600</v>
+      </c>
+      <c r="J31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" t="s">
+        <v>145</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32">
+        <v>1600</v>
+      </c>
+      <c r="J32" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" t="s">
+        <v>151</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33">
+        <v>960</v>
+      </c>
+      <c r="J33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>154</v>
+      </c>
+      <c r="F34" t="s">
+        <v>155</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34">
+        <v>21250</v>
+      </c>
+      <c r="J34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>157</v>
+      </c>
+      <c r="G35" t="s">
+        <v>158</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35">
+        <v>360</v>
+      </c>
+      <c r="J35" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36" t="s">
+        <v>158</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36">
+        <v>360</v>
+      </c>
+      <c r="J36" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>162</v>
+      </c>
+      <c r="G37" t="s">
+        <v>158</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37">
+        <v>360</v>
+      </c>
+      <c r="J37" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66558FD-7E80-465C-A7C3-BF037CFEC601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485845C1-19B8-46E8-B70A-1C9A89B3623A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="158">
   <si>
     <t>Responsável</t>
   </si>
@@ -55,451 +55,433 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>LP-047032</t>
+  </si>
+  <si>
+    <t>3418260604</t>
+  </si>
+  <si>
+    <t>Retificar Arrastador e topo Pistão LE</t>
+  </si>
+  <si>
+    <t>COR4CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE12</t>
+  </si>
+  <si>
+    <t>LP-060252</t>
+  </si>
+  <si>
+    <t>Rafael Lima</t>
+  </si>
+  <si>
+    <t>685907</t>
+  </si>
+  <si>
+    <t>4725800244</t>
+  </si>
+  <si>
+    <t>EXECUTAR IMPRESSÃO 3D</t>
+  </si>
+  <si>
+    <t>SOC2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-A</t>
+  </si>
+  <si>
+    <t>LP-060253</t>
+  </si>
+  <si>
+    <t>Cadastrado</t>
+  </si>
+  <si>
+    <t>685486</t>
+  </si>
+  <si>
+    <t>4729111811</t>
+  </si>
+  <si>
+    <t>DISCO DE ARRASTE ZEMA</t>
+  </si>
+  <si>
+    <t>SIU5CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>LP-060255</t>
+  </si>
+  <si>
+    <t>6855008</t>
+  </si>
+  <si>
+    <t>4729111796</t>
+  </si>
+  <si>
+    <t>Retrabalho dispostivo HPC</t>
+  </si>
+  <si>
+    <t>MMA5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW11-C</t>
+  </si>
+  <si>
+    <t>LP-060256</t>
+  </si>
+  <si>
+    <t>685617</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>4717600141</t>
+  </si>
+  <si>
+    <t>OLH2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE31</t>
+  </si>
+  <si>
+    <t>LP-060257</t>
+  </si>
+  <si>
+    <t>4717600101</t>
+  </si>
+  <si>
+    <t>LP-060258</t>
+  </si>
+  <si>
+    <t>4717600132</t>
+  </si>
+  <si>
+    <t>LP-060259</t>
+  </si>
+  <si>
+    <t>BM-00108513_002_00000018</t>
+  </si>
+  <si>
+    <t>N.A</t>
+  </si>
+  <si>
+    <t>FCu retifica</t>
+  </si>
+  <si>
+    <t>FOM2CT</t>
+  </si>
+  <si>
+    <t>CtP/ETS</t>
+  </si>
+  <si>
+    <t>LP-060261</t>
+  </si>
+  <si>
+    <t>685552</t>
+  </si>
+  <si>
+    <t>4710800278</t>
+  </si>
+  <si>
+    <t>685552 - Retrabalho Ponto ZEMA (Valvula)</t>
+  </si>
+  <si>
+    <t>VIM2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE11</t>
+  </si>
+  <si>
+    <t>LP-060262</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>685411</t>
+  </si>
+  <si>
+    <t>4729111452</t>
+  </si>
+  <si>
+    <t>DU 685411 Pino torno benzinger placa nov</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
     <t>CtP/TEF11</t>
   </si>
   <si>
-    <t>Yesica Gonzalez</t>
+    <t>LP-060263</t>
+  </si>
+  <si>
+    <t>4729105567_POS 1</t>
+  </si>
+  <si>
+    <t>DU 685411 POSIÇÃO 1 da Placa silberhorn</t>
+  </si>
+  <si>
+    <t>LP-060264</t>
+  </si>
+  <si>
+    <t>4710101475</t>
+  </si>
+  <si>
+    <t>DU 685411 Garra d Pinça H.Rebaixada HTT</t>
+  </si>
+  <si>
+    <t>LP-060265</t>
+  </si>
+  <si>
+    <t>4710800193</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto Haste Cheia U.D</t>
+  </si>
+  <si>
+    <t>LP-060266</t>
+  </si>
+  <si>
+    <t>4710800199</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto retífica Bhamulle</t>
+  </si>
+  <si>
+    <t>LP-060267</t>
+  </si>
+  <si>
+    <t>685615</t>
+  </si>
+  <si>
+    <t>4729107091</t>
+  </si>
+  <si>
+    <t>Anel Interno Atmo</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>LP-060268</t>
+  </si>
+  <si>
+    <t>4741420045</t>
+  </si>
+  <si>
+    <t>Ponteira de Medição</t>
+  </si>
+  <si>
+    <t>LP-060269</t>
+  </si>
+  <si>
+    <t>685703</t>
+  </si>
+  <si>
+    <t>4719241071</t>
+  </si>
+  <si>
+    <t>REBOLO LCMV</t>
+  </si>
+  <si>
+    <t>REGIMARA</t>
+  </si>
+  <si>
+    <t>LP-060273</t>
+  </si>
+  <si>
+    <t>685554</t>
+  </si>
+  <si>
+    <t>4702900326</t>
+  </si>
+  <si>
+    <t>PINO DE CONTATO ELETRODO</t>
+  </si>
+  <si>
+    <t>LP-060274</t>
+  </si>
+  <si>
+    <t>4712001839</t>
+  </si>
+  <si>
+    <t>Garra</t>
   </si>
   <si>
     <t>DOUGLAS</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>CtP/MFE31</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>LP-060280</t>
+  </si>
+  <si>
+    <t>685553</t>
+  </si>
+  <si>
+    <t>471090069</t>
+  </si>
+  <si>
+    <t>Ponteira</t>
+  </si>
+  <si>
+    <t>LP-060281</t>
+  </si>
+  <si>
+    <t>4729106006</t>
+  </si>
+  <si>
+    <t>Bujão ZPD</t>
+  </si>
+  <si>
+    <t>LP-060282</t>
+  </si>
+  <si>
+    <t>685664</t>
+  </si>
+  <si>
+    <t>BASE DA CAIXA</t>
+  </si>
+  <si>
+    <t>BRUNO ARAUJO</t>
+  </si>
+  <si>
+    <t>LP-060283</t>
+  </si>
+  <si>
+    <t>TAMPA DA CAIXA</t>
+  </si>
+  <si>
+    <t>LP-060284</t>
+  </si>
+  <si>
+    <t>685622</t>
+  </si>
+  <si>
+    <t>SUPORTE SP</t>
+  </si>
+  <si>
+    <t>TKC1CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS21-BR</t>
+  </si>
+  <si>
+    <t>LP-060289</t>
+  </si>
+  <si>
+    <t>SUPORTE SPS</t>
+  </si>
+  <si>
+    <t>LP-060290</t>
+  </si>
+  <si>
+    <t>685606</t>
+  </si>
+  <si>
+    <t>4729110910</t>
+  </si>
+  <si>
+    <t>Vedação st.120 - pos 02</t>
+  </si>
+  <si>
+    <t>ZAK2CT</t>
+  </si>
+  <si>
+    <t>LP-060293</t>
+  </si>
+  <si>
+    <t>685541</t>
+  </si>
+  <si>
+    <t>4730502020</t>
+  </si>
+  <si>
+    <t>Pino guia</t>
+  </si>
+  <si>
+    <t>LP-060294</t>
+  </si>
+  <si>
+    <t>4711500224</t>
+  </si>
+  <si>
+    <t>DU 685411 Pino HTT 23352 QUEBRADO.</t>
+  </si>
+  <si>
+    <t>LP-060295</t>
+  </si>
+  <si>
+    <t>4728603019</t>
+  </si>
+  <si>
+    <t>Haste st. 10 - pos 04</t>
+  </si>
+  <si>
+    <t>LP-060296</t>
+  </si>
+  <si>
+    <t>4728701153</t>
+  </si>
+  <si>
+    <t>Crin 1/2</t>
+  </si>
+  <si>
+    <t>ANF2CT</t>
+  </si>
+  <si>
+    <t>LP-060299</t>
+  </si>
+  <si>
+    <t>Crin 3</t>
+  </si>
+  <si>
+    <t>LP-060300</t>
   </si>
   <si>
     <t>Renato Meira</t>
   </si>
   <si>
+    <t>Criação de desenho</t>
+  </si>
+  <si>
+    <t>IAP3CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE21</t>
+  </si>
+  <si>
+    <t>LP-060315</t>
+  </si>
+  <si>
+    <t>685401</t>
+  </si>
+  <si>
+    <t>4729109899/BB5504</t>
+  </si>
+  <si>
+    <t>Expulsor</t>
+  </si>
+  <si>
+    <t>LP-060316</t>
+  </si>
+  <si>
+    <t>Roda do separador CRIN3 - BH8000</t>
+  </si>
+  <si>
+    <t>HENRIQUE O.</t>
+  </si>
+  <si>
+    <t>LP-060318</t>
+  </si>
+  <si>
     <t>685616</t>
-  </si>
-  <si>
-    <t>CtP/MFE21</t>
-  </si>
-  <si>
-    <t>Marcelo Simoes</t>
-  </si>
-  <si>
-    <t>LP-047032</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>3418260604</t>
-  </si>
-  <si>
-    <t>Retificar Arrastador e topo Pistão LE</t>
-  </si>
-  <si>
-    <t>COR4CT</t>
-  </si>
-  <si>
-    <t>CtP/MFE12</t>
-  </si>
-  <si>
-    <t>LP-060252</t>
-  </si>
-  <si>
-    <t>Rafael Lima</t>
-  </si>
-  <si>
-    <t>685907</t>
-  </si>
-  <si>
-    <t>4725800244</t>
-  </si>
-  <si>
-    <t>EXECUTAR IMPRESSÃO 3D</t>
-  </si>
-  <si>
-    <t>SOC2CT</t>
-  </si>
-  <si>
-    <t>CtP/MFW12-A</t>
-  </si>
-  <si>
-    <t>LP-060253</t>
-  </si>
-  <si>
-    <t>685486</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>4729111811</t>
-  </si>
-  <si>
-    <t>DISCO DE ARRASTE ZEMA</t>
-  </si>
-  <si>
-    <t>SIU5CT</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS23-BR</t>
-  </si>
-  <si>
-    <t>LP-060255</t>
-  </si>
-  <si>
-    <t>6855008</t>
-  </si>
-  <si>
-    <t>4729111796</t>
-  </si>
-  <si>
-    <t>Retrabalho dispostivo HPC</t>
-  </si>
-  <si>
-    <t>MMA5CT</t>
-  </si>
-  <si>
-    <t>CtP/MFW11-C</t>
-  </si>
-  <si>
-    <t>LP-060256</t>
-  </si>
-  <si>
-    <t>685617</t>
-  </si>
-  <si>
-    <t>4717600141</t>
-  </si>
-  <si>
-    <t>OLH2CT</t>
-  </si>
-  <si>
-    <t>LP-060257</t>
-  </si>
-  <si>
-    <t>4717600101</t>
-  </si>
-  <si>
-    <t>LP-060258</t>
-  </si>
-  <si>
-    <t>4717600132</t>
-  </si>
-  <si>
-    <t>LP-060259</t>
-  </si>
-  <si>
-    <t>BM-00108513_002_00000018</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>N.A</t>
-  </si>
-  <si>
-    <t>FCu retifica</t>
-  </si>
-  <si>
-    <t>FOM2CT</t>
-  </si>
-  <si>
-    <t>CtP/ETS</t>
-  </si>
-  <si>
-    <t>LP-060261</t>
-  </si>
-  <si>
-    <t>685552</t>
-  </si>
-  <si>
-    <t>4710800278</t>
-  </si>
-  <si>
-    <t>685552 - Retrabalho Ponto ZEMA (Valvula)</t>
-  </si>
-  <si>
-    <t>VIM2CT</t>
-  </si>
-  <si>
-    <t>CtP/MFE11</t>
-  </si>
-  <si>
-    <t>LP-060262</t>
-  </si>
-  <si>
-    <t>685411</t>
-  </si>
-  <si>
-    <t>4729111452</t>
-  </si>
-  <si>
-    <t>DU 685411 Pino torno benzinger placa nov</t>
-  </si>
-  <si>
-    <t>DONI- 2803</t>
-  </si>
-  <si>
-    <t>LP-060263</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>4729105567_POS 1</t>
-  </si>
-  <si>
-    <t>DU 685411 POSIÇÃO 1 da Placa silberhorn</t>
-  </si>
-  <si>
-    <t>LP-060264</t>
-  </si>
-  <si>
-    <t>4710101475</t>
-  </si>
-  <si>
-    <t>DU 685411 Garra d Pinça H.Rebaixada HTT</t>
-  </si>
-  <si>
-    <t>LP-060265</t>
-  </si>
-  <si>
-    <t>4710800193</t>
-  </si>
-  <si>
-    <t>DU 685411 Contra ponto Haste Cheia U.D</t>
-  </si>
-  <si>
-    <t>LP-060266</t>
-  </si>
-  <si>
-    <t>4710800199</t>
-  </si>
-  <si>
-    <t>DU 685411 Contra ponto retífica Bhamulle</t>
-  </si>
-  <si>
-    <t>LP-060267</t>
-  </si>
-  <si>
-    <t>685615</t>
-  </si>
-  <si>
-    <t>4729107091</t>
-  </si>
-  <si>
-    <t>Anel Interno Atmo</t>
-  </si>
-  <si>
-    <t>FERNANDA A</t>
-  </si>
-  <si>
-    <t>LP-060268</t>
-  </si>
-  <si>
-    <t>4741420045</t>
-  </si>
-  <si>
-    <t>Ponteira de Medição</t>
-  </si>
-  <si>
-    <t>LP-060269</t>
-  </si>
-  <si>
-    <t>685703</t>
-  </si>
-  <si>
-    <t>4719241071</t>
-  </si>
-  <si>
-    <t>REBOLO LCMV</t>
-  </si>
-  <si>
-    <t>REGIMARA</t>
-  </si>
-  <si>
-    <t>LP-060273</t>
-  </si>
-  <si>
-    <t>685554</t>
-  </si>
-  <si>
-    <t>4702900326</t>
-  </si>
-  <si>
-    <t>PINO DE CONTATO ELETRODO</t>
-  </si>
-  <si>
-    <t>LP-060274</t>
-  </si>
-  <si>
-    <t>4712001839</t>
-  </si>
-  <si>
-    <t>Garra</t>
-  </si>
-  <si>
-    <t>LP-060280</t>
-  </si>
-  <si>
-    <t>685553</t>
-  </si>
-  <si>
-    <t>471090069</t>
-  </si>
-  <si>
-    <t>Ponteira</t>
-  </si>
-  <si>
-    <t>LP-060281</t>
-  </si>
-  <si>
-    <t>4729106006</t>
-  </si>
-  <si>
-    <t>Bujão ZPD</t>
-  </si>
-  <si>
-    <t>LP-060282</t>
-  </si>
-  <si>
-    <t>685664</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>BASE DA CAIXA</t>
-  </si>
-  <si>
-    <t>BRUNO ARAUJO</t>
-  </si>
-  <si>
-    <t>LP-060283</t>
-  </si>
-  <si>
-    <t>TAMPA DA CAIXA</t>
-  </si>
-  <si>
-    <t>LP-060284</t>
-  </si>
-  <si>
-    <t>685622</t>
-  </si>
-  <si>
-    <t>SUPORTE SP</t>
-  </si>
-  <si>
-    <t>TKC1CT</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS21-BR</t>
-  </si>
-  <si>
-    <t>LP-060289</t>
-  </si>
-  <si>
-    <t>SUPORTE SPS</t>
-  </si>
-  <si>
-    <t>LP-060290</t>
-  </si>
-  <si>
-    <t>685606</t>
-  </si>
-  <si>
-    <t>4729110910</t>
-  </si>
-  <si>
-    <t>Vedação st.120 - pos 02</t>
-  </si>
-  <si>
-    <t>ZAK2CT</t>
-  </si>
-  <si>
-    <t>LP-060293</t>
-  </si>
-  <si>
-    <t>685541</t>
-  </si>
-  <si>
-    <t>4730502020</t>
-  </si>
-  <si>
-    <t>Pino guia</t>
-  </si>
-  <si>
-    <t>LP-060294</t>
-  </si>
-  <si>
-    <t>4711500224</t>
-  </si>
-  <si>
-    <t>DU 685411 Pino HTT 23352 QUEBRADO.</t>
-  </si>
-  <si>
-    <t>LP-060295</t>
-  </si>
-  <si>
-    <t>4728603019</t>
-  </si>
-  <si>
-    <t>Haste st. 10 - pos 04</t>
-  </si>
-  <si>
-    <t>LP-060296</t>
-  </si>
-  <si>
-    <t>4728701153</t>
-  </si>
-  <si>
-    <t>Crin 1/2</t>
-  </si>
-  <si>
-    <t>ANF2CT</t>
-  </si>
-  <si>
-    <t>LP-060299</t>
-  </si>
-  <si>
-    <t>Crin 3</t>
-  </si>
-  <si>
-    <t>LP-060300</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Criação de desenho</t>
-  </si>
-  <si>
-    <t>IAP3CT</t>
-  </si>
-  <si>
-    <t>LP-060315</t>
-  </si>
-  <si>
-    <t>685401</t>
-  </si>
-  <si>
-    <t>4729109899/BB5504</t>
-  </si>
-  <si>
-    <t>Expulsor</t>
-  </si>
-  <si>
-    <t>LP-060316</t>
-  </si>
-  <si>
-    <t>Roda do separador CRIN3 - BH8000</t>
-  </si>
-  <si>
-    <t>HENRIQUE O.</t>
-  </si>
-  <si>
-    <t>LP-060318</t>
   </si>
   <si>
     <t>Criação de norma e desenho batente</t>
@@ -864,7 +846,7 @@
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -904,1154 +886,1250 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
       </c>
       <c r="D2">
         <v>400</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I2">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
       </c>
       <c r="D3">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I3">
         <v>540</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I4">
         <v>720</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I5">
         <v>500</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
       </c>
       <c r="D6">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I6">
         <v>12000</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
       </c>
       <c r="D7">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I7">
         <v>12000</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
       </c>
       <c r="D8">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I8">
         <v>12000</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="I9">
         <v>500</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I10">
         <v>300</v>
       </c>
       <c r="J10" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
+        <v>61</v>
+      </c>
+      <c r="C11">
+        <v>19</v>
       </c>
       <c r="D11">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I11">
         <v>3400</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I12">
         <v>1100</v>
       </c>
       <c r="J12" t="s">
-        <v>77</v>
+        <v>69</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
+        <v>61</v>
+      </c>
+      <c r="C13">
+        <v>19</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I13">
         <v>4720</v>
       </c>
       <c r="J13" t="s">
-        <v>80</v>
+        <v>72</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
+        <v>61</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I14">
         <v>4400</v>
       </c>
       <c r="J14" t="s">
-        <v>83</v>
+        <v>75</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
+        <v>61</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I15">
         <v>2640</v>
       </c>
       <c r="J15" t="s">
-        <v>86</v>
+        <v>78</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>16</v>
+        <v>79</v>
+      </c>
+      <c r="C16">
+        <v>19</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I16">
         <v>2500</v>
       </c>
       <c r="J16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
+        <v>79</v>
+      </c>
+      <c r="C17">
+        <v>19</v>
       </c>
       <c r="D17">
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I17">
         <v>1020</v>
       </c>
       <c r="J17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
+        <v>87</v>
+      </c>
+      <c r="C18">
+        <v>19</v>
       </c>
       <c r="D18">
         <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I18">
         <v>1760</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
+        <v>92</v>
+      </c>
+      <c r="C19">
+        <v>19</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I19">
         <v>13800</v>
       </c>
       <c r="J19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
+        <v>54</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H20" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I20">
         <v>4000</v>
       </c>
       <c r="J20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="C21">
+        <v>19</v>
       </c>
       <c r="D21">
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I21">
         <v>1500</v>
       </c>
       <c r="J21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="K21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>19</v>
       </c>
       <c r="D22">
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I22">
         <v>3300</v>
       </c>
       <c r="J22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
+        <v>107</v>
+      </c>
+      <c r="C23">
+        <v>19</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" t="s">
-        <v>115</v>
-      </c>
       <c r="F23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I23">
         <v>230</v>
       </c>
       <c r="J23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" t="s">
-        <v>16</v>
+        <v>107</v>
+      </c>
+      <c r="C24">
+        <v>19</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" t="s">
-        <v>115</v>
-      </c>
       <c r="F24" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G24" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I24">
         <v>445</v>
       </c>
       <c r="J24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
+        <v>113</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H25" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I25">
         <v>225</v>
       </c>
       <c r="J25" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="K25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" t="s">
-        <v>22</v>
+        <v>113</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I26">
         <v>180</v>
       </c>
       <c r="J26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="K26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
+        <v>120</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
       </c>
       <c r="D27">
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H27" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I27">
         <v>1100</v>
       </c>
       <c r="J27" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="K27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" t="s">
-        <v>16</v>
+        <v>125</v>
+      </c>
+      <c r="C28">
+        <v>19</v>
       </c>
       <c r="D28">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I28">
         <v>1120</v>
       </c>
       <c r="J28" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="K28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29">
         <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G29" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I29">
         <v>1000</v>
       </c>
       <c r="J29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="K29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
+        <v>120</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H30" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I30">
         <v>4300</v>
       </c>
       <c r="J30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="K30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>16</v>
+        <v>79</v>
+      </c>
+      <c r="C31">
+        <v>19</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I31">
         <v>1600</v>
       </c>
       <c r="J31" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="K31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>16</v>
+        <v>79</v>
+      </c>
+      <c r="C32">
+        <v>19</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
-      <c r="E32" t="s">
-        <v>115</v>
-      </c>
       <c r="F32" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G32" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I32">
         <v>1600</v>
       </c>
       <c r="J32" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="K32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" t="s">
-        <v>36</v>
+        <v>61</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
-      <c r="E33" t="s">
-        <v>149</v>
-      </c>
       <c r="F33" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G33" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H33" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="I33">
         <v>960</v>
       </c>
       <c r="J33" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="K33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" t="s">
-        <v>16</v>
+        <v>146</v>
+      </c>
+      <c r="C34">
+        <v>19</v>
       </c>
       <c r="D34">
         <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I34">
         <v>21250</v>
       </c>
       <c r="J34" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="K34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>16</v>
+        <v>79</v>
+      </c>
+      <c r="C35">
+        <v>19</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F35" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G35" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H35" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I35">
         <v>360</v>
       </c>
       <c r="J35" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="K35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" t="s">
-        <v>16</v>
+        <v>153</v>
+      </c>
+      <c r="C36">
+        <v>19</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G36" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I36">
         <v>360</v>
       </c>
       <c r="J36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="K36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>16</v>
+        <v>79</v>
+      </c>
+      <c r="C37">
+        <v>19</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G37" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H37" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I37">
         <v>360</v>
       </c>
       <c r="J37" t="s">
-        <v>163</v>
+        <v>157</v>
+      </c>
+      <c r="K37" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4503CA9-8065-4158-95A2-48758FBE555A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7516ABC9-A086-4A5D-B1FB-2CF6ECAABFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="428">
   <si>
     <t>Responsável</t>
   </si>
@@ -91,21 +104,6 @@
     <t>Thais Fischer</t>
   </si>
   <si>
-    <t>685605</t>
-  </si>
-  <si>
-    <t>Retrabalho Grupo Magnético</t>
-  </si>
-  <si>
-    <t>CAH2CT</t>
-  </si>
-  <si>
-    <t>CtP/MFW32-A</t>
-  </si>
-  <si>
-    <t>LP-060335</t>
-  </si>
-  <si>
     <t>Edson Bento</t>
   </si>
   <si>
@@ -133,21 +131,12 @@
     <t>685433</t>
   </si>
   <si>
-    <t>4738360388-0070</t>
-  </si>
-  <si>
-    <t>OGIVA</t>
-  </si>
-  <si>
     <t>QMM</t>
   </si>
   <si>
     <t>PS/QMM7-CtP</t>
   </si>
   <si>
-    <t>LP-060337</t>
-  </si>
-  <si>
     <t>0414Y10192-01</t>
   </si>
   <si>
@@ -169,9 +158,6 @@
     <t>LP-060338</t>
   </si>
   <si>
-    <t>Cadastrado parcial</t>
-  </si>
-  <si>
     <t>0414Y10193-01</t>
   </si>
   <si>
@@ -673,24 +659,9 @@
     <t>Renato Meira</t>
   </si>
   <si>
-    <t>6856134</t>
-  </si>
-  <si>
-    <t>A/D</t>
-  </si>
-  <si>
-    <t>ARRASTADOR ARRUELA F00VC10400</t>
-  </si>
-  <si>
-    <t>R. CHLAD</t>
-  </si>
-  <si>
     <t>CtP/MFE31</t>
   </si>
   <si>
-    <t>LP-060402</t>
-  </si>
-  <si>
     <t>685555</t>
   </si>
   <si>
@@ -817,7 +788,535 @@
     <t>LP-060415</t>
   </si>
   <si>
-    <t>Cadastrado</t>
+    <t>LP-060420</t>
+  </si>
+  <si>
+    <t>LP-060421</t>
+  </si>
+  <si>
+    <t>LP-060422</t>
+  </si>
+  <si>
+    <t>LP-060423</t>
+  </si>
+  <si>
+    <t>LP-060424</t>
+  </si>
+  <si>
+    <t>LP-060426</t>
+  </si>
+  <si>
+    <t>LP-060427</t>
+  </si>
+  <si>
+    <t>LP-060428</t>
+  </si>
+  <si>
+    <t>LP-060429</t>
+  </si>
+  <si>
+    <t>LP-060430</t>
+  </si>
+  <si>
+    <t>LP-060431</t>
+  </si>
+  <si>
+    <t>LP-060432</t>
+  </si>
+  <si>
+    <t>LP-060433</t>
+  </si>
+  <si>
+    <t>LP-060434</t>
+  </si>
+  <si>
+    <t>LP-060435</t>
+  </si>
+  <si>
+    <t>LP-060436</t>
+  </si>
+  <si>
+    <t>LP-060437</t>
+  </si>
+  <si>
+    <t>LP-060438</t>
+  </si>
+  <si>
+    <t>LP-060439</t>
+  </si>
+  <si>
+    <t>LP-060440</t>
+  </si>
+  <si>
+    <t>LP-060441</t>
+  </si>
+  <si>
+    <t>LP-060442</t>
+  </si>
+  <si>
+    <t>LP-060443</t>
+  </si>
+  <si>
+    <t>LP-060444</t>
+  </si>
+  <si>
+    <t>LP-060445</t>
+  </si>
+  <si>
+    <t>LP-060446</t>
+  </si>
+  <si>
+    <t>LP-060447</t>
+  </si>
+  <si>
+    <t>LP-060448</t>
+  </si>
+  <si>
+    <t>LP-060449</t>
+  </si>
+  <si>
+    <t>LP-060450</t>
+  </si>
+  <si>
+    <t>LP-060452</t>
+  </si>
+  <si>
+    <t>LP-060453</t>
+  </si>
+  <si>
+    <t>LP-060454</t>
+  </si>
+  <si>
+    <t>LP-060455</t>
+  </si>
+  <si>
+    <t>LP-060456</t>
+  </si>
+  <si>
+    <t>LP-060458</t>
+  </si>
+  <si>
+    <t>LP-060459</t>
+  </si>
+  <si>
+    <t>LP-060460</t>
+  </si>
+  <si>
+    <t>LP-060461</t>
+  </si>
+  <si>
+    <t>LP-060462</t>
+  </si>
+  <si>
+    <t>LP-060463</t>
+  </si>
+  <si>
+    <t>LP-060464</t>
+  </si>
+  <si>
+    <t>LP-060465</t>
+  </si>
+  <si>
+    <t>LP-060466</t>
+  </si>
+  <si>
+    <t>LP-060467</t>
+  </si>
+  <si>
+    <t>LP-060468</t>
+  </si>
+  <si>
+    <t>LP-060469</t>
+  </si>
+  <si>
+    <t>LP-060470</t>
+  </si>
+  <si>
+    <t>LP-060471</t>
+  </si>
+  <si>
+    <t>LP-060472</t>
+  </si>
+  <si>
+    <t>LP-060473</t>
+  </si>
+  <si>
+    <t>LP-060474</t>
+  </si>
+  <si>
+    <t>LP-060475</t>
+  </si>
+  <si>
+    <t>LP-060476</t>
+  </si>
+  <si>
+    <t>LP-060477</t>
+  </si>
+  <si>
+    <t>LP-060478</t>
+  </si>
+  <si>
+    <t>LP-060479</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>685541</t>
+  </si>
+  <si>
+    <t>4730502018</t>
+  </si>
+  <si>
+    <t>Pino guia</t>
+  </si>
+  <si>
+    <t>685533</t>
+  </si>
+  <si>
+    <t>4712004047</t>
+  </si>
+  <si>
+    <t>4727501447</t>
+  </si>
+  <si>
+    <t>Posição 3</t>
+  </si>
+  <si>
+    <t>685531</t>
+  </si>
+  <si>
+    <t>4722802008</t>
+  </si>
+  <si>
+    <t>Carimbo</t>
+  </si>
+  <si>
+    <t>685486</t>
+  </si>
+  <si>
+    <t>4729.111.811</t>
+  </si>
+  <si>
+    <t>IP-685486 SISTEMA DE ARRASTE CILINDRO H</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>685482</t>
+  </si>
+  <si>
+    <t>4705900688_POS 3</t>
+  </si>
+  <si>
+    <t>IP 685482 POS 3 DO MAGAZINE MIKRON U.D</t>
+  </si>
+  <si>
+    <t>685491</t>
+  </si>
+  <si>
+    <t>4711202060_POS 9</t>
+  </si>
+  <si>
+    <t>IP-685491 POSIÇÃO 9 Folha 10(Mola Slee.)</t>
+  </si>
+  <si>
+    <t>4710101504</t>
+  </si>
+  <si>
+    <t>IP 685486 Pinça ∅11 Zema 4593 EL H</t>
+  </si>
+  <si>
+    <t>685487</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>4710800216</t>
+  </si>
+  <si>
+    <t>IP 685487 Contra ponto Zema cilindro A</t>
+  </si>
+  <si>
+    <t>4710800217</t>
+  </si>
+  <si>
+    <t>4710800168</t>
+  </si>
+  <si>
+    <t>4727501440</t>
+  </si>
+  <si>
+    <t>Dispositivo Famup</t>
+  </si>
+  <si>
+    <t>TAT2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-A</t>
+  </si>
+  <si>
+    <t>4711801483</t>
+  </si>
+  <si>
+    <t>Mandris IP</t>
+  </si>
+  <si>
+    <t>685546</t>
+  </si>
+  <si>
+    <t>4711401154</t>
+  </si>
+  <si>
+    <t>Castanha Item 1 folha 2</t>
+  </si>
+  <si>
+    <t>Castanha item 3 folha 4</t>
+  </si>
+  <si>
+    <t>4711401157</t>
+  </si>
+  <si>
+    <t>Castanha item 2 folha 3</t>
+  </si>
+  <si>
+    <t>Batente item 3 folha 4</t>
+  </si>
+  <si>
+    <t>4711401155</t>
+  </si>
+  <si>
+    <t>4711401156</t>
+  </si>
+  <si>
+    <t>685484</t>
+  </si>
+  <si>
+    <t>4711401298</t>
+  </si>
+  <si>
+    <t>IP 685484 Garra de fixação d pistões LE</t>
+  </si>
+  <si>
+    <t>4710.800.338</t>
+  </si>
+  <si>
+    <t>IP 685484 Contra Ponto IP-LE</t>
+  </si>
+  <si>
+    <t>4710.800.340</t>
+  </si>
+  <si>
+    <t>IP 685484 Suporte de Ponto IP-LE</t>
+  </si>
+  <si>
+    <t>4711100131_POS 1</t>
+  </si>
+  <si>
+    <t>IP 685484 POSIÇÃO 1   Arrastador LE</t>
+  </si>
+  <si>
+    <t>4711100131_POS 2</t>
+  </si>
+  <si>
+    <t>4729110286</t>
+  </si>
+  <si>
+    <t>IP 685484 Disp. Espaçador de rebolo LE</t>
+  </si>
+  <si>
+    <t>685485</t>
+  </si>
+  <si>
+    <t>4710101534</t>
+  </si>
+  <si>
+    <t>LE 685485 Pino de fixação de peça IP-LE</t>
+  </si>
+  <si>
+    <t>108513_008</t>
+  </si>
+  <si>
+    <t>Dispositivo prensagem para UPCRS</t>
+  </si>
+  <si>
+    <t>ROB2CT</t>
+  </si>
+  <si>
+    <t>PS-DC/ENS1-LA</t>
+  </si>
+  <si>
+    <t>685606</t>
+  </si>
+  <si>
+    <t>0804144741</t>
+  </si>
+  <si>
+    <t>Retrabalho disp. st 120</t>
+  </si>
+  <si>
+    <t>ZAK2CT</t>
+  </si>
+  <si>
+    <t>685601490852</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>4664500156</t>
+  </si>
+  <si>
+    <t>PINO REFRIGERAÇÃO NAKAMURA</t>
+  </si>
+  <si>
+    <t>JAC1JVL</t>
+  </si>
+  <si>
+    <t>685601490357</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>4304800227</t>
+  </si>
+  <si>
+    <t>IP 685484 Rebolo borazon Pistão P</t>
+  </si>
+  <si>
+    <t>4304800267</t>
+  </si>
+  <si>
+    <t>4719270025</t>
+  </si>
+  <si>
+    <t>4729401812</t>
+  </si>
+  <si>
+    <t>IP 685485 Bucha de recolhimento Ø12 P7</t>
+  </si>
+  <si>
+    <t>4719266046</t>
+  </si>
+  <si>
+    <t>4304800229</t>
+  </si>
+  <si>
+    <t>4304800262</t>
+  </si>
+  <si>
+    <t>4304800434</t>
+  </si>
+  <si>
+    <t>4711401159</t>
+  </si>
+  <si>
+    <t>DU 685411 Garra torno Benzinger HR00240C</t>
+  </si>
+  <si>
+    <t>685009</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4729111603</t>
+  </si>
+  <si>
+    <t>Confecção posição P007</t>
+  </si>
+  <si>
+    <t>YOI1CT</t>
+  </si>
+  <si>
+    <t>Confecção posição P009</t>
+  </si>
+  <si>
+    <t>4705900362</t>
+  </si>
+  <si>
+    <t>Espelho do suporte de AGIE</t>
+  </si>
+  <si>
+    <t>CRI4CT</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Acrylic cover</t>
+  </si>
+  <si>
+    <t>PRG3CT</t>
+  </si>
+  <si>
+    <t>PS/ESY2-LA</t>
+  </si>
+  <si>
+    <t>Cover Holder</t>
+  </si>
+  <si>
+    <t>Arrastador (Gear pump dragger) c/ pino</t>
+  </si>
+  <si>
+    <t>33010</t>
+  </si>
+  <si>
+    <t>Rolamento 33010-The TImkenCompany-3D-06-</t>
+  </si>
+  <si>
+    <t>33110</t>
+  </si>
+  <si>
+    <t>Rolamento 33110 - TIMKEN Tapered Roller</t>
+  </si>
+  <si>
+    <t>685664</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SUPORTE 104MM</t>
+  </si>
+  <si>
+    <t>BRUNO ARAUJO</t>
+  </si>
+  <si>
+    <t>SUPORTE 130MM</t>
+  </si>
+  <si>
+    <t>SUPORTE 165MM</t>
+  </si>
+  <si>
+    <t>4729110936</t>
+  </si>
+  <si>
+    <t>Posição 2</t>
+  </si>
+  <si>
+    <t>DESENHO</t>
+  </si>
+  <si>
+    <t>Dispositivos HTT</t>
+  </si>
+  <si>
+    <t>JULIANA MELO</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
@@ -1165,17 +1664,17 @@
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -1251,40 +1750,40 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2">
+        <v>1200</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="N2" t="s">
         <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2">
-        <v>200</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -1293,60 +1792,57 @@
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U2">
         <v>36000</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>309</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I3">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>265</v>
+        <v>46</v>
       </c>
       <c r="M3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -1355,60 +1851,57 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U3">
         <v>0.01</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>310</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I4">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -1417,60 +1910,57 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="R4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="S4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U4">
         <v>0.01</v>
       </c>
       <c r="V4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>310</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I5">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1479,60 +1969,57 @@
         <v>2</v>
       </c>
       <c r="Q5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="R5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="S5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U5">
         <v>0.01</v>
       </c>
       <c r="V5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>310</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I6">
         <v>400</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="M6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1541,60 +2028,57 @@
         <v>4</v>
       </c>
       <c r="Q6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U6">
         <v>0.01</v>
       </c>
       <c r="V6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>310</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>400</v>
       </c>
       <c r="J7" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="M7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1603,60 +2087,57 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="R7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U7">
         <v>0.01</v>
       </c>
       <c r="V7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>310</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I8">
         <v>400</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K8" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1665,60 +2146,57 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="R8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U8">
         <v>0.01</v>
       </c>
       <c r="V8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>309</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I9">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="M9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1727,60 +2205,57 @@
         <v>3</v>
       </c>
       <c r="Q9" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U9">
         <v>0.01</v>
       </c>
       <c r="V9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>310</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I10">
-        <v>400</v>
+        <v>2600</v>
       </c>
       <c r="J10" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="M10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1789,60 +2264,57 @@
         <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="R10" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="S10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T10" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U10">
         <v>0.01</v>
       </c>
       <c r="V10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>310</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I11">
-        <v>800</v>
+        <v>2600</v>
       </c>
       <c r="J11" t="s">
-        <v>90</v>
-      </c>
-      <c r="K11" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="M11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1851,60 +2323,57 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="R11" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U11">
         <v>0.01</v>
       </c>
       <c r="V11" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>310</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I12">
         <v>2600</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="M12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1913,60 +2382,57 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="R12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="S12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U12">
         <v>0.01</v>
       </c>
       <c r="V12" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>310</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I13">
         <v>2600</v>
       </c>
       <c r="J13" t="s">
-        <v>101</v>
-      </c>
-      <c r="K13" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="M13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1975,60 +2441,57 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="R13" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U13">
         <v>0.01</v>
       </c>
       <c r="V13" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>310</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I14">
         <v>2600</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
-      </c>
-      <c r="K14" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -2037,60 +2500,57 @@
         <v>2</v>
       </c>
       <c r="Q14" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="R14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="S14" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U14">
         <v>0.01</v>
       </c>
       <c r="V14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>310</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I15">
         <v>2600</v>
       </c>
       <c r="J15" t="s">
-        <v>111</v>
-      </c>
-      <c r="K15" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="M15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -2099,1048 +2559,991 @@
         <v>4</v>
       </c>
       <c r="Q15" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="R15" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="S15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U15">
         <v>0.01</v>
       </c>
       <c r="V15" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16">
-        <v>4</v>
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>310</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I16">
         <v>2600</v>
       </c>
       <c r="J16" t="s">
-        <v>116</v>
-      </c>
-      <c r="K16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="M16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s">
+        <v>372</v>
+      </c>
+      <c r="O16" t="s">
+        <v>309</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>313</v>
+      </c>
+      <c r="R16" t="s">
+        <v>373</v>
+      </c>
+      <c r="S16" t="s">
+        <v>374</v>
+      </c>
+      <c r="T16" t="s">
+        <v>375</v>
+      </c>
+      <c r="U16">
+        <v>2000</v>
+      </c>
+      <c r="V16" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>310</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I17">
         <v>2600</v>
       </c>
       <c r="J17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18">
+        <v>600</v>
+      </c>
+      <c r="J18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19">
+        <v>4600</v>
+      </c>
+      <c r="J19" t="s">
         <v>118</v>
       </c>
-      <c r="K17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
         <v>119</v>
       </c>
-      <c r="F18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18">
-        <v>2600</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="C20" t="s">
+        <v>310</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
         <v>120</v>
       </c>
-      <c r="K18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F20" t="s">
         <v>121</v>
       </c>
-      <c r="F19" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19">
-        <v>2600</v>
-      </c>
-      <c r="J19" t="s">
-        <v>122</v>
-      </c>
-      <c r="K19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" t="s">
-        <v>89</v>
-      </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I20">
         <v>600</v>
       </c>
       <c r="J20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
+        <v>310</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
         <v>124</v>
       </c>
-      <c r="K20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21">
+        <v>800</v>
+      </c>
+      <c r="J21" t="s">
         <v>125</v>
       </c>
-      <c r="F21" t="s">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>310</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
         <v>126</v>
       </c>
-      <c r="G21" t="s">
-        <v>39</v>
-      </c>
-      <c r="H21" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21">
-        <v>4600</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="F22" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22">
+        <v>2500</v>
+      </c>
+      <c r="J22" t="s">
         <v>127</v>
       </c>
-      <c r="K21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
         <v>128</v>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23">
+        <v>300</v>
+      </c>
+      <c r="J23" t="s">
         <v>129</v>
       </c>
-      <c r="F22" t="s">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
         <v>130</v>
       </c>
-      <c r="G22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H22" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22">
+      <c r="F24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24">
         <v>600</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J24" t="s">
         <v>131</v>
       </c>
-      <c r="K22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>310</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
         <v>132</v>
       </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F25" t="s">
         <v>133</v>
       </c>
-      <c r="F23" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" t="s">
-        <v>39</v>
-      </c>
-      <c r="H23" t="s">
-        <v>40</v>
-      </c>
-      <c r="I23">
-        <v>800</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25">
+        <v>600</v>
+      </c>
+      <c r="J25" t="s">
         <v>134</v>
       </c>
-      <c r="K23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
         <v>135</v>
       </c>
-      <c r="F24" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24">
+      <c r="C26" t="s">
+        <v>310</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26">
+        <v>400</v>
+      </c>
+      <c r="J26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27">
+        <v>500</v>
+      </c>
+      <c r="J27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>310</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28">
+        <v>500</v>
+      </c>
+      <c r="J28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>310</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29">
         <v>2500</v>
       </c>
-      <c r="J24" t="s">
-        <v>136</v>
-      </c>
-      <c r="K24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F25" t="s">
-        <v>130</v>
-      </c>
-      <c r="G25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25">
-        <v>300</v>
-      </c>
-      <c r="J25" t="s">
-        <v>138</v>
-      </c>
-      <c r="K25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>139</v>
-      </c>
-      <c r="F26" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" t="s">
-        <v>39</v>
-      </c>
-      <c r="H26" t="s">
-        <v>40</v>
-      </c>
-      <c r="I26">
-        <v>600</v>
-      </c>
-      <c r="J26" t="s">
-        <v>140</v>
-      </c>
-      <c r="K26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>141</v>
-      </c>
-      <c r="F27" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" t="s">
-        <v>39</v>
-      </c>
-      <c r="H27" t="s">
-        <v>40</v>
-      </c>
-      <c r="I27">
-        <v>600</v>
-      </c>
-      <c r="J27" t="s">
-        <v>143</v>
-      </c>
-      <c r="K27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="J29" t="s">
         <v>145</v>
       </c>
-      <c r="F28" t="s">
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
         <v>146</v>
       </c>
-      <c r="G28" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28">
-        <v>400</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="F30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30">
+        <v>2500</v>
+      </c>
+      <c r="J30" t="s">
         <v>147</v>
       </c>
-      <c r="K28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
+        <v>310</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
         <v>148</v>
       </c>
-      <c r="F29" t="s">
-        <v>149</v>
-      </c>
-      <c r="G29" t="s">
-        <v>39</v>
-      </c>
-      <c r="H29" t="s">
-        <v>40</v>
-      </c>
-      <c r="I29">
-        <v>500</v>
-      </c>
-      <c r="J29" t="s">
-        <v>150</v>
-      </c>
-      <c r="K29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" t="s">
-        <v>149</v>
-      </c>
-      <c r="G30" t="s">
-        <v>39</v>
-      </c>
-      <c r="H30" t="s">
-        <v>40</v>
-      </c>
-      <c r="I30">
-        <v>500</v>
-      </c>
-      <c r="J30" t="s">
-        <v>152</v>
-      </c>
-      <c r="K30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>153</v>
-      </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H31" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I31">
         <v>2500</v>
       </c>
       <c r="J31" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>310</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32">
+        <v>800</v>
+      </c>
+      <c r="J32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>310</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33">
+        <v>500</v>
+      </c>
+      <c r="J33" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
         <v>154</v>
       </c>
-      <c r="K31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F34" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34">
+        <v>500</v>
+      </c>
+      <c r="J34" t="s">
         <v>155</v>
       </c>
-      <c r="F32" t="s">
-        <v>95</v>
-      </c>
-      <c r="G32" t="s">
-        <v>39</v>
-      </c>
-      <c r="H32" t="s">
-        <v>40</v>
-      </c>
-      <c r="I32">
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" t="s">
+        <v>310</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>156</v>
+      </c>
+      <c r="F35" t="s">
+        <v>86</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35">
         <v>2500</v>
       </c>
-      <c r="J32" t="s">
-        <v>156</v>
-      </c>
-      <c r="K32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="J35" t="s">
         <v>157</v>
       </c>
-      <c r="F33" t="s">
-        <v>95</v>
-      </c>
-      <c r="G33" t="s">
-        <v>39</v>
-      </c>
-      <c r="H33" t="s">
-        <v>40</v>
-      </c>
-      <c r="I33">
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>310</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F36" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36">
         <v>2500</v>
       </c>
-      <c r="J33" t="s">
-        <v>158</v>
-      </c>
-      <c r="K33" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="J36" t="s">
         <v>159</v>
       </c>
-      <c r="F34" t="s">
-        <v>130</v>
-      </c>
-      <c r="G34" t="s">
-        <v>39</v>
-      </c>
-      <c r="H34" t="s">
-        <v>40</v>
-      </c>
-      <c r="I34">
-        <v>800</v>
-      </c>
-      <c r="J34" t="s">
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" t="s">
+        <v>310</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
         <v>160</v>
       </c>
-      <c r="K34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35" t="s">
-        <v>39</v>
-      </c>
-      <c r="H35" t="s">
-        <v>40</v>
-      </c>
-      <c r="I35">
-        <v>500</v>
-      </c>
-      <c r="J35" t="s">
-        <v>162</v>
-      </c>
-      <c r="K35" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36">
-        <v>4</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>163</v>
-      </c>
-      <c r="F36" t="s">
-        <v>61</v>
-      </c>
-      <c r="G36" t="s">
-        <v>39</v>
-      </c>
-      <c r="H36" t="s">
-        <v>40</v>
-      </c>
-      <c r="I36">
-        <v>500</v>
-      </c>
-      <c r="J36" t="s">
-        <v>164</v>
-      </c>
-      <c r="K36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>165</v>
-      </c>
       <c r="F37" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H37" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I37">
         <v>2500</v>
       </c>
       <c r="J37" t="s">
-        <v>166</v>
-      </c>
-      <c r="K37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>310</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H38" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I38">
         <v>2500</v>
       </c>
       <c r="J38" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>310</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>164</v>
+      </c>
+      <c r="F39" t="s">
+        <v>86</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39">
+        <v>2600</v>
+      </c>
+      <c r="J39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" t="s">
+        <v>308</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
         <v>168</v>
       </c>
-      <c r="K38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F40" t="s">
         <v>169</v>
       </c>
-      <c r="F39" t="s">
-        <v>95</v>
-      </c>
-      <c r="G39" t="s">
-        <v>39</v>
-      </c>
-      <c r="H39" t="s">
-        <v>40</v>
-      </c>
-      <c r="I39">
-        <v>2500</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="G40" t="s">
         <v>170</v>
       </c>
-      <c r="K39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="H40" t="s">
         <v>171</v>
       </c>
-      <c r="F40" t="s">
-        <v>95</v>
-      </c>
-      <c r="G40" t="s">
-        <v>39</v>
-      </c>
-      <c r="H40" t="s">
-        <v>40</v>
-      </c>
       <c r="I40">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="J40" t="s">
         <v>172</v>
       </c>
-      <c r="K40" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>166</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41">
-        <v>4</v>
+        <v>173</v>
+      </c>
+      <c r="C41" t="s">
+        <v>311</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="G41" t="s">
-        <v>39</v>
+        <v>176</v>
       </c>
       <c r="H41" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="I41">
-        <v>2600</v>
+        <v>12000</v>
       </c>
       <c r="J41" t="s">
-        <v>174</v>
-      </c>
-      <c r="K41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>176</v>
-      </c>
-      <c r="C42">
-        <v>6</v>
+        <v>179</v>
+      </c>
+      <c r="C42" t="s">
+        <v>309</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F42" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G42" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H42" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I42">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J42" t="s">
-        <v>181</v>
-      </c>
-      <c r="K42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B43" t="s">
-        <v>182</v>
-      </c>
-      <c r="C43">
+        <v>186</v>
+      </c>
+      <c r="C43" t="s">
+        <v>312</v>
+      </c>
+      <c r="D43">
         <v>3</v>
       </c>
-      <c r="D43">
-        <v>15</v>
-      </c>
       <c r="E43" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F43" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G43" t="s">
+        <v>189</v>
+      </c>
+      <c r="H43" t="s">
+        <v>190</v>
+      </c>
+      <c r="I43">
+        <v>1200</v>
+      </c>
+      <c r="J43" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>185</v>
       </c>
-      <c r="H43" t="s">
+      <c r="B44" t="s">
+        <v>192</v>
+      </c>
+      <c r="C44" t="s">
+        <v>312</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>193</v>
+      </c>
+      <c r="F44" t="s">
+        <v>194</v>
+      </c>
+      <c r="G44" t="s">
+        <v>189</v>
+      </c>
+      <c r="H44" t="s">
+        <v>190</v>
+      </c>
+      <c r="I44">
+        <v>660</v>
+      </c>
+      <c r="J44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" t="s">
         <v>186</v>
       </c>
-      <c r="I43">
-        <v>12000</v>
-      </c>
-      <c r="J43" t="s">
-        <v>187</v>
-      </c>
-      <c r="K43" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" t="s">
-        <v>188</v>
-      </c>
-      <c r="C44">
-        <v>5</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" t="s">
-        <v>190</v>
-      </c>
-      <c r="G44" t="s">
-        <v>191</v>
-      </c>
-      <c r="H44" t="s">
-        <v>192</v>
-      </c>
-      <c r="I44">
-        <v>2000</v>
-      </c>
-      <c r="J44" t="s">
-        <v>193</v>
-      </c>
-      <c r="K44" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>194</v>
-      </c>
-      <c r="B45" t="s">
-        <v>195</v>
-      </c>
-      <c r="C45">
-        <v>19</v>
+      <c r="C45" t="s">
+        <v>312</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -3149,176 +3552,161 @@
         <v>196</v>
       </c>
       <c r="F45" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G45" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H45" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I45">
         <v>1200</v>
       </c>
       <c r="J45" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" t="s">
+        <v>309</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="E46" t="s">
+        <v>198</v>
+      </c>
+      <c r="F46" t="s">
+        <v>199</v>
+      </c>
+      <c r="G46" t="s">
+        <v>182</v>
+      </c>
+      <c r="H46" t="s">
         <v>200</v>
       </c>
-      <c r="K45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>194</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="I46">
+        <v>9000</v>
+      </c>
+      <c r="J46" t="s">
         <v>201</v>
       </c>
-      <c r="C46">
-        <v>19</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" t="s">
+        <v>192</v>
+      </c>
+      <c r="C47" t="s">
+        <v>309</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47" t="s">
         <v>202</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F47" t="s">
         <v>203</v>
       </c>
-      <c r="G46" t="s">
-        <v>198</v>
-      </c>
-      <c r="H46" t="s">
-        <v>199</v>
-      </c>
-      <c r="I46">
-        <v>660</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="G47" t="s">
         <v>204</v>
       </c>
-      <c r="K46" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>194</v>
-      </c>
-      <c r="B47" t="s">
-        <v>195</v>
-      </c>
-      <c r="C47">
-        <v>19</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="H47" t="s">
         <v>205</v>
       </c>
-      <c r="F47" t="s">
-        <v>197</v>
-      </c>
-      <c r="G47" t="s">
-        <v>198</v>
-      </c>
-      <c r="H47" t="s">
-        <v>199</v>
-      </c>
       <c r="I47">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="J47" t="s">
         <v>206</v>
       </c>
-      <c r="K47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
-      </c>
-      <c r="C48">
-        <v>5</v>
+        <v>209</v>
+      </c>
+      <c r="C48" t="s">
+        <v>312</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F48" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G48" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H48" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="I48">
-        <v>9000</v>
+        <v>4600</v>
       </c>
       <c r="J48" t="s">
-        <v>210</v>
-      </c>
-      <c r="K48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C49">
-        <v>5</v>
+        <v>213</v>
+      </c>
+      <c r="C49" t="s">
+        <v>312</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F49" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G49" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="H49" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="I49">
-        <v>4000</v>
+        <v>3150</v>
       </c>
       <c r="J49" t="s">
-        <v>215</v>
-      </c>
-      <c r="K49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
         <v>217</v>
       </c>
-      <c r="C50">
-        <v>19</v>
+      <c r="C50" t="s">
+        <v>312</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" t="s">
         <v>218</v>
@@ -3327,433 +3715,2096 @@
         <v>219</v>
       </c>
       <c r="G50" t="s">
+        <v>189</v>
+      </c>
+      <c r="H50" t="s">
+        <v>190</v>
+      </c>
+      <c r="I50">
+        <v>1200</v>
+      </c>
+      <c r="J50" t="s">
         <v>220</v>
       </c>
-      <c r="H50" t="s">
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>221</v>
       </c>
-      <c r="I50">
-        <v>600</v>
-      </c>
-      <c r="J50" t="s">
+      <c r="B51" t="s">
         <v>222</v>
       </c>
-      <c r="K50" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>194</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>309</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51" t="s">
         <v>223</v>
       </c>
-      <c r="C51">
-        <v>19</v>
-      </c>
-      <c r="D51">
+      <c r="F51" t="s">
+        <v>224</v>
+      </c>
+      <c r="G51" t="s">
+        <v>182</v>
+      </c>
+      <c r="H51" t="s">
+        <v>183</v>
+      </c>
+      <c r="I51">
+        <v>225</v>
+      </c>
+      <c r="J51" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" t="s">
+        <v>226</v>
+      </c>
+      <c r="C52" t="s">
+        <v>312</v>
+      </c>
+      <c r="D52">
         <v>4</v>
       </c>
-      <c r="E51" t="s">
-        <v>224</v>
-      </c>
-      <c r="F51" t="s">
-        <v>225</v>
-      </c>
-      <c r="G51" t="s">
-        <v>198</v>
-      </c>
-      <c r="H51" t="s">
-        <v>199</v>
-      </c>
-      <c r="I51">
-        <v>4600</v>
-      </c>
-      <c r="J51" t="s">
-        <v>226</v>
-      </c>
-      <c r="K51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>194</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="E52" t="s">
         <v>227</v>
       </c>
-      <c r="C52">
-        <v>19</v>
-      </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>228</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" t="s">
+        <v>190</v>
+      </c>
+      <c r="I52">
+        <v>800</v>
+      </c>
+      <c r="J52" t="s">
         <v>229</v>
       </c>
-      <c r="G52" t="s">
-        <v>198</v>
-      </c>
-      <c r="H52" t="s">
-        <v>199</v>
-      </c>
-      <c r="I52">
-        <v>3150</v>
-      </c>
-      <c r="J52" t="s">
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>221</v>
+      </c>
+      <c r="B53" t="s">
         <v>230</v>
       </c>
-      <c r="K52" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>194</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>312</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
         <v>231</v>
       </c>
-      <c r="C53">
-        <v>19</v>
-      </c>
-      <c r="D53">
-        <v>3</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>232</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>233</v>
       </c>
-      <c r="G53" t="s">
-        <v>198</v>
-      </c>
       <c r="H53" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="I53">
-        <v>1200</v>
+        <v>270</v>
       </c>
       <c r="J53" t="s">
         <v>234</v>
       </c>
-      <c r="K53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" t="s">
         <v>235</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
+        <v>309</v>
+      </c>
+      <c r="D54">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
         <v>236</v>
       </c>
-      <c r="C54">
-        <v>5</v>
-      </c>
-      <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>237</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>238</v>
       </c>
-      <c r="G54" t="s">
-        <v>191</v>
-      </c>
       <c r="H54" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I54">
-        <v>225</v>
+        <v>450</v>
       </c>
       <c r="J54" t="s">
         <v>239</v>
       </c>
-      <c r="K54" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="B55" t="s">
+        <v>235</v>
+      </c>
+      <c r="C55" t="s">
+        <v>309</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>236</v>
+      </c>
+      <c r="F55" t="s">
         <v>240</v>
       </c>
-      <c r="C55">
-        <v>19</v>
-      </c>
-      <c r="D55">
+      <c r="G55" t="s">
+        <v>238</v>
+      </c>
+      <c r="H55" t="s">
+        <v>183</v>
+      </c>
+      <c r="I55">
+        <v>500</v>
+      </c>
+      <c r="J55" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" t="s">
+        <v>235</v>
+      </c>
+      <c r="C56" t="s">
+        <v>309</v>
+      </c>
+      <c r="D56">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>242</v>
+      </c>
+      <c r="F56" t="s">
+        <v>237</v>
+      </c>
+      <c r="G56" t="s">
+        <v>238</v>
+      </c>
+      <c r="H56" t="s">
+        <v>183</v>
+      </c>
+      <c r="I56">
+        <v>450</v>
+      </c>
+      <c r="J56" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" t="s">
+        <v>235</v>
+      </c>
+      <c r="C57" t="s">
+        <v>309</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>242</v>
+      </c>
+      <c r="F57" t="s">
+        <v>240</v>
+      </c>
+      <c r="G57" t="s">
+        <v>238</v>
+      </c>
+      <c r="H57" t="s">
+        <v>183</v>
+      </c>
+      <c r="I57">
+        <v>500</v>
+      </c>
+      <c r="J57" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" t="s">
+        <v>245</v>
+      </c>
+      <c r="C58" t="s">
+        <v>312</v>
+      </c>
+      <c r="D58">
+        <v>50</v>
+      </c>
+      <c r="E58" t="s">
+        <v>313</v>
+      </c>
+      <c r="F58" t="s">
+        <v>246</v>
+      </c>
+      <c r="G58" t="s">
+        <v>247</v>
+      </c>
+      <c r="H58" t="s">
+        <v>183</v>
+      </c>
+      <c r="I58">
+        <v>2750</v>
+      </c>
+      <c r="J58" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" t="s">
+        <v>245</v>
+      </c>
+      <c r="C59" t="s">
+        <v>312</v>
+      </c>
+      <c r="D59">
+        <v>50</v>
+      </c>
+      <c r="E59" t="s">
+        <v>313</v>
+      </c>
+      <c r="F59" t="s">
+        <v>249</v>
+      </c>
+      <c r="G59" t="s">
+        <v>247</v>
+      </c>
+      <c r="H59" t="s">
+        <v>183</v>
+      </c>
+      <c r="I59">
+        <v>2750</v>
+      </c>
+      <c r="J59" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" t="s">
+        <v>314</v>
+      </c>
+      <c r="C60" t="s">
+        <v>312</v>
+      </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60" t="s">
+        <v>315</v>
+      </c>
+      <c r="F60" t="s">
+        <v>316</v>
+      </c>
+      <c r="G60" t="s">
+        <v>189</v>
+      </c>
+      <c r="H60" t="s">
+        <v>190</v>
+      </c>
+      <c r="I60">
+        <v>4000</v>
+      </c>
+      <c r="J60" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>185</v>
+      </c>
+      <c r="B61" t="s">
+        <v>317</v>
+      </c>
+      <c r="C61" t="s">
+        <v>312</v>
+      </c>
+      <c r="D61">
+        <v>60</v>
+      </c>
+      <c r="E61" t="s">
+        <v>318</v>
+      </c>
+      <c r="F61" t="s">
+        <v>219</v>
+      </c>
+      <c r="G61" t="s">
+        <v>189</v>
+      </c>
+      <c r="H61" t="s">
+        <v>190</v>
+      </c>
+      <c r="I61">
+        <v>6600</v>
+      </c>
+      <c r="J61" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" t="s">
+        <v>314</v>
+      </c>
+      <c r="C62" t="s">
+        <v>312</v>
+      </c>
+      <c r="D62">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>319</v>
+      </c>
+      <c r="F62" t="s">
+        <v>320</v>
+      </c>
+      <c r="G62" t="s">
+        <v>189</v>
+      </c>
+      <c r="H62" t="s">
+        <v>190</v>
+      </c>
+      <c r="I62">
+        <v>14040</v>
+      </c>
+      <c r="J62" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" t="s">
+        <v>321</v>
+      </c>
+      <c r="C63" t="s">
+        <v>312</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63" t="s">
+        <v>322</v>
+      </c>
+      <c r="F63" t="s">
+        <v>323</v>
+      </c>
+      <c r="G63" t="s">
+        <v>189</v>
+      </c>
+      <c r="H63" t="s">
+        <v>190</v>
+      </c>
+      <c r="I63">
+        <v>800</v>
+      </c>
+      <c r="J63" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>221</v>
+      </c>
+      <c r="B64" t="s">
+        <v>324</v>
+      </c>
+      <c r="C64" t="s">
+        <v>312</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64" t="s">
+        <v>325</v>
+      </c>
+      <c r="F64" t="s">
+        <v>326</v>
+      </c>
+      <c r="G64" t="s">
+        <v>327</v>
+      </c>
+      <c r="H64" t="s">
+        <v>190</v>
+      </c>
+      <c r="I64">
+        <v>720</v>
+      </c>
+      <c r="J64" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" t="s">
+        <v>328</v>
+      </c>
+      <c r="C65" t="s">
+        <v>312</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>329</v>
+      </c>
+      <c r="F65" t="s">
+        <v>330</v>
+      </c>
+      <c r="G65" t="s">
+        <v>327</v>
+      </c>
+      <c r="H65" t="s">
+        <v>190</v>
+      </c>
+      <c r="I65">
+        <v>4300</v>
+      </c>
+      <c r="J65" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" t="s">
+        <v>331</v>
+      </c>
+      <c r="C66" t="s">
+        <v>312</v>
+      </c>
+      <c r="D66">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>332</v>
+      </c>
+      <c r="F66" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66" t="s">
+        <v>327</v>
+      </c>
+      <c r="H66" t="s">
+        <v>190</v>
+      </c>
+      <c r="I66">
+        <v>1000</v>
+      </c>
+      <c r="J66" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>185</v>
+      </c>
+      <c r="B67" t="s">
+        <v>324</v>
+      </c>
+      <c r="C67" t="s">
+        <v>312</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>334</v>
+      </c>
+      <c r="F67" t="s">
+        <v>335</v>
+      </c>
+      <c r="G67" t="s">
+        <v>327</v>
+      </c>
+      <c r="H67" t="s">
+        <v>190</v>
+      </c>
+      <c r="I67">
+        <v>2850</v>
+      </c>
+      <c r="J67" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" t="s">
+        <v>336</v>
+      </c>
+      <c r="C68" t="s">
+        <v>337</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>338</v>
+      </c>
+      <c r="F68" t="s">
+        <v>339</v>
+      </c>
+      <c r="G68" t="s">
+        <v>327</v>
+      </c>
+      <c r="H68" t="s">
+        <v>190</v>
+      </c>
+      <c r="I68">
+        <v>660</v>
+      </c>
+      <c r="J68" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" t="s">
+        <v>336</v>
+      </c>
+      <c r="C69" t="s">
+        <v>337</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>340</v>
+      </c>
+      <c r="F69" t="s">
+        <v>339</v>
+      </c>
+      <c r="G69" t="s">
+        <v>327</v>
+      </c>
+      <c r="H69" t="s">
+        <v>190</v>
+      </c>
+      <c r="I69">
+        <v>660</v>
+      </c>
+      <c r="J69" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>185</v>
+      </c>
+      <c r="B70" t="s">
+        <v>336</v>
+      </c>
+      <c r="C70" t="s">
+        <v>337</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>341</v>
+      </c>
+      <c r="F70" t="s">
+        <v>339</v>
+      </c>
+      <c r="G70" t="s">
+        <v>327</v>
+      </c>
+      <c r="H70" t="s">
+        <v>190</v>
+      </c>
+      <c r="I70">
+        <v>660</v>
+      </c>
+      <c r="J70" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s">
+        <v>314</v>
+      </c>
+      <c r="C71" t="s">
+        <v>312</v>
+      </c>
+      <c r="D71">
+        <v>12</v>
+      </c>
+      <c r="E71" t="s">
+        <v>342</v>
+      </c>
+      <c r="F71" t="s">
+        <v>343</v>
+      </c>
+      <c r="G71" t="s">
+        <v>344</v>
+      </c>
+      <c r="H71" t="s">
+        <v>345</v>
+      </c>
+      <c r="I71">
+        <v>12000</v>
+      </c>
+      <c r="J71" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" t="s">
+        <v>328</v>
+      </c>
+      <c r="C72" t="s">
+        <v>312</v>
+      </c>
+      <c r="D72">
         <v>4</v>
       </c>
-      <c r="E55" t="s">
-        <v>241</v>
-      </c>
-      <c r="F55" t="s">
-        <v>242</v>
-      </c>
-      <c r="G55" t="s">
-        <v>198</v>
-      </c>
-      <c r="H55" t="s">
-        <v>199</v>
-      </c>
-      <c r="I55">
-        <v>800</v>
-      </c>
-      <c r="J55" t="s">
-        <v>243</v>
-      </c>
-      <c r="K55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>235</v>
-      </c>
-      <c r="B56" t="s">
-        <v>244</v>
-      </c>
-      <c r="C56">
-        <v>19</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" t="s">
-        <v>245</v>
-      </c>
-      <c r="F56" t="s">
-        <v>246</v>
-      </c>
-      <c r="G56" t="s">
-        <v>247</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="E72" t="s">
+        <v>346</v>
+      </c>
+      <c r="F72" t="s">
+        <v>347</v>
+      </c>
+      <c r="G72" t="s">
+        <v>344</v>
+      </c>
+      <c r="H72" t="s">
+        <v>345</v>
+      </c>
+      <c r="I72">
+        <v>1000</v>
+      </c>
+      <c r="J72" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" t="s">
+        <v>348</v>
+      </c>
+      <c r="C73" t="s">
+        <v>312</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73" t="s">
+        <v>349</v>
+      </c>
+      <c r="F73" t="s">
+        <v>350</v>
+      </c>
+      <c r="G73" t="s">
+        <v>344</v>
+      </c>
+      <c r="H73" t="s">
+        <v>345</v>
+      </c>
+      <c r="I73">
+        <v>8280</v>
+      </c>
+      <c r="J73" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B74" t="s">
+        <v>348</v>
+      </c>
+      <c r="C74" t="s">
+        <v>312</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74" t="s">
+        <v>349</v>
+      </c>
+      <c r="F74" t="s">
+        <v>351</v>
+      </c>
+      <c r="G74" t="s">
+        <v>344</v>
+      </c>
+      <c r="H74" t="s">
+        <v>345</v>
+      </c>
+      <c r="I74">
+        <v>8280</v>
+      </c>
+      <c r="J74" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" t="s">
+        <v>348</v>
+      </c>
+      <c r="C75" t="s">
+        <v>312</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>352</v>
+      </c>
+      <c r="F75" t="s">
+        <v>350</v>
+      </c>
+      <c r="G75" t="s">
+        <v>344</v>
+      </c>
+      <c r="H75" t="s">
+        <v>345</v>
+      </c>
+      <c r="I75">
+        <v>7080</v>
+      </c>
+      <c r="J75" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>185</v>
+      </c>
+      <c r="B76" t="s">
+        <v>348</v>
+      </c>
+      <c r="C76" t="s">
+        <v>312</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>352</v>
+      </c>
+      <c r="F76" t="s">
+        <v>353</v>
+      </c>
+      <c r="G76" t="s">
+        <v>344</v>
+      </c>
+      <c r="H76" t="s">
+        <v>345</v>
+      </c>
+      <c r="I76">
+        <v>7080</v>
+      </c>
+      <c r="J76" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>185</v>
+      </c>
+      <c r="B77" t="s">
+        <v>348</v>
+      </c>
+      <c r="C77" t="s">
+        <v>312</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>352</v>
+      </c>
+      <c r="F77" t="s">
+        <v>354</v>
+      </c>
+      <c r="G77" t="s">
+        <v>344</v>
+      </c>
+      <c r="H77" t="s">
+        <v>345</v>
+      </c>
+      <c r="I77">
+        <v>3900</v>
+      </c>
+      <c r="J77" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>185</v>
+      </c>
+      <c r="B78" t="s">
+        <v>348</v>
+      </c>
+      <c r="C78" t="s">
+        <v>312</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>355</v>
+      </c>
+      <c r="F78" t="s">
+        <v>350</v>
+      </c>
+      <c r="G78" t="s">
+        <v>344</v>
+      </c>
+      <c r="H78" t="s">
+        <v>345</v>
+      </c>
+      <c r="I78">
+        <v>7500</v>
+      </c>
+      <c r="J78" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>185</v>
+      </c>
+      <c r="B79" t="s">
+        <v>348</v>
+      </c>
+      <c r="C79" t="s">
+        <v>312</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>355</v>
+      </c>
+      <c r="F79" t="s">
+        <v>353</v>
+      </c>
+      <c r="G79" t="s">
+        <v>344</v>
+      </c>
+      <c r="H79" t="s">
+        <v>345</v>
+      </c>
+      <c r="I79">
+        <v>9120</v>
+      </c>
+      <c r="J79" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>185</v>
+      </c>
+      <c r="B80" t="s">
+        <v>348</v>
+      </c>
+      <c r="C80" t="s">
+        <v>312</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>355</v>
+      </c>
+      <c r="F80" t="s">
+        <v>354</v>
+      </c>
+      <c r="G80" t="s">
+        <v>344</v>
+      </c>
+      <c r="H80" t="s">
+        <v>345</v>
+      </c>
+      <c r="I80">
+        <v>4500</v>
+      </c>
+      <c r="J80" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>185</v>
+      </c>
+      <c r="B81" t="s">
+        <v>348</v>
+      </c>
+      <c r="C81" t="s">
+        <v>312</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81" t="s">
+        <v>356</v>
+      </c>
+      <c r="F81" t="s">
+        <v>350</v>
+      </c>
+      <c r="G81" t="s">
+        <v>344</v>
+      </c>
+      <c r="H81" t="s">
+        <v>345</v>
+      </c>
+      <c r="I81">
+        <v>8100</v>
+      </c>
+      <c r="J81" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" t="s">
+        <v>348</v>
+      </c>
+      <c r="C82" t="s">
+        <v>312</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82" t="s">
+        <v>356</v>
+      </c>
+      <c r="F82" t="s">
+        <v>353</v>
+      </c>
+      <c r="G82" t="s">
+        <v>344</v>
+      </c>
+      <c r="H82" t="s">
+        <v>345</v>
+      </c>
+      <c r="I82">
+        <v>8100</v>
+      </c>
+      <c r="J82" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>185</v>
+      </c>
+      <c r="B83" t="s">
+        <v>348</v>
+      </c>
+      <c r="C83" t="s">
+        <v>312</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+      <c r="E83" t="s">
+        <v>356</v>
+      </c>
+      <c r="F83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G83" t="s">
+        <v>344</v>
+      </c>
+      <c r="H83" t="s">
+        <v>345</v>
+      </c>
+      <c r="I83">
+        <v>4500</v>
+      </c>
+      <c r="J83" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" t="s">
+        <v>357</v>
+      </c>
+      <c r="C84" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84" t="s">
+        <v>358</v>
+      </c>
+      <c r="F84" t="s">
+        <v>359</v>
+      </c>
+      <c r="G84" t="s">
+        <v>327</v>
+      </c>
+      <c r="H84" t="s">
+        <v>190</v>
+      </c>
+      <c r="I84">
+        <v>5880</v>
+      </c>
+      <c r="J84" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>185</v>
+      </c>
+      <c r="B85" t="s">
+        <v>357</v>
+      </c>
+      <c r="C85" t="s">
+        <v>312</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>360</v>
+      </c>
+      <c r="F85" t="s">
+        <v>361</v>
+      </c>
+      <c r="G85" t="s">
+        <v>327</v>
+      </c>
+      <c r="H85" t="s">
+        <v>190</v>
+      </c>
+      <c r="I85">
+        <v>3000</v>
+      </c>
+      <c r="J85" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>185</v>
+      </c>
+      <c r="B86" t="s">
+        <v>357</v>
+      </c>
+      <c r="C86" t="s">
+        <v>312</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>362</v>
+      </c>
+      <c r="F86" t="s">
+        <v>363</v>
+      </c>
+      <c r="G86" t="s">
+        <v>327</v>
+      </c>
+      <c r="H86" t="s">
+        <v>190</v>
+      </c>
+      <c r="I86">
+        <v>3000</v>
+      </c>
+      <c r="J86" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>185</v>
+      </c>
+      <c r="B87" t="s">
+        <v>357</v>
+      </c>
+      <c r="C87" t="s">
+        <v>312</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87" t="s">
+        <v>364</v>
+      </c>
+      <c r="F87" t="s">
+        <v>365</v>
+      </c>
+      <c r="G87" t="s">
+        <v>327</v>
+      </c>
+      <c r="H87" t="s">
+        <v>190</v>
+      </c>
+      <c r="I87">
+        <v>1340</v>
+      </c>
+      <c r="J87" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>185</v>
+      </c>
+      <c r="B88" t="s">
+        <v>357</v>
+      </c>
+      <c r="C88" t="s">
+        <v>312</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88" t="s">
+        <v>366</v>
+      </c>
+      <c r="F88" t="s">
+        <v>365</v>
+      </c>
+      <c r="G88" t="s">
+        <v>327</v>
+      </c>
+      <c r="H88" t="s">
+        <v>190</v>
+      </c>
+      <c r="I88">
+        <v>940</v>
+      </c>
+      <c r="J88" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>185</v>
+      </c>
+      <c r="B89" t="s">
+        <v>357</v>
+      </c>
+      <c r="C89" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89" t="s">
+        <v>367</v>
+      </c>
+      <c r="F89" t="s">
+        <v>368</v>
+      </c>
+      <c r="G89" t="s">
+        <v>327</v>
+      </c>
+      <c r="H89" t="s">
+        <v>190</v>
+      </c>
+      <c r="I89">
+        <v>1480</v>
+      </c>
+      <c r="J89" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>185</v>
+      </c>
+      <c r="B90" t="s">
+        <v>369</v>
+      </c>
+      <c r="C90" t="s">
+        <v>312</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90" t="s">
+        <v>370</v>
+      </c>
+      <c r="F90" t="s">
+        <v>371</v>
+      </c>
+      <c r="G90" t="s">
+        <v>327</v>
+      </c>
+      <c r="H90" t="s">
+        <v>190</v>
+      </c>
+      <c r="I90">
+        <v>6940</v>
+      </c>
+      <c r="J90" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" t="s">
+        <v>376</v>
+      </c>
+      <c r="C91" t="s">
+        <v>309</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+      <c r="E91" t="s">
+        <v>377</v>
+      </c>
+      <c r="F91" t="s">
+        <v>378</v>
+      </c>
+      <c r="G91" t="s">
+        <v>379</v>
+      </c>
+      <c r="H91" t="s">
+        <v>183</v>
+      </c>
+      <c r="I91">
+        <v>300</v>
+      </c>
+      <c r="J91" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>166</v>
+      </c>
+      <c r="B92" t="s">
+        <v>380</v>
+      </c>
+      <c r="C92" t="s">
+        <v>381</v>
+      </c>
+      <c r="D92">
+        <v>9</v>
+      </c>
+      <c r="E92" t="s">
+        <v>382</v>
+      </c>
+      <c r="F92" t="s">
+        <v>383</v>
+      </c>
+      <c r="G92" t="s">
+        <v>384</v>
+      </c>
+      <c r="H92" t="s">
+        <v>183</v>
+      </c>
+      <c r="I92">
+        <v>900</v>
+      </c>
+      <c r="J92" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>166</v>
+      </c>
+      <c r="B93" t="s">
+        <v>385</v>
+      </c>
+      <c r="C93" t="s">
+        <v>381</v>
+      </c>
+      <c r="D93">
+        <v>10</v>
+      </c>
+      <c r="E93" t="s">
+        <v>382</v>
+      </c>
+      <c r="F93" t="s">
+        <v>383</v>
+      </c>
+      <c r="G93" t="s">
+        <v>384</v>
+      </c>
+      <c r="H93" t="s">
+        <v>183</v>
+      </c>
+      <c r="I93">
+        <v>8000</v>
+      </c>
+      <c r="J93" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>185</v>
+      </c>
+      <c r="B94" t="s">
+        <v>357</v>
+      </c>
+      <c r="C94" t="s">
+        <v>386</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>387</v>
+      </c>
+      <c r="F94" t="s">
+        <v>388</v>
+      </c>
+      <c r="G94" t="s">
+        <v>327</v>
+      </c>
+      <c r="H94" t="s">
+        <v>190</v>
+      </c>
+      <c r="I94">
+        <v>130</v>
+      </c>
+      <c r="J94" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B95" t="s">
+        <v>357</v>
+      </c>
+      <c r="C95" t="s">
+        <v>386</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95" t="s">
+        <v>389</v>
+      </c>
+      <c r="F95" t="s">
+        <v>388</v>
+      </c>
+      <c r="G95" t="s">
+        <v>327</v>
+      </c>
+      <c r="H95" t="s">
+        <v>190</v>
+      </c>
+      <c r="I95">
+        <v>330</v>
+      </c>
+      <c r="J95" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" t="s">
+        <v>357</v>
+      </c>
+      <c r="C96" t="s">
+        <v>386</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96" t="s">
+        <v>390</v>
+      </c>
+      <c r="F96" t="s">
+        <v>388</v>
+      </c>
+      <c r="G96" t="s">
+        <v>327</v>
+      </c>
+      <c r="H96" t="s">
+        <v>190</v>
+      </c>
+      <c r="I96">
+        <v>260</v>
+      </c>
+      <c r="J96" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>185</v>
+      </c>
+      <c r="B97" t="s">
+        <v>369</v>
+      </c>
+      <c r="C97" t="s">
+        <v>312</v>
+      </c>
+      <c r="D97">
+        <v>3</v>
+      </c>
+      <c r="E97" t="s">
+        <v>391</v>
+      </c>
+      <c r="F97" t="s">
+        <v>392</v>
+      </c>
+      <c r="G97" t="s">
+        <v>327</v>
+      </c>
+      <c r="H97" t="s">
+        <v>190</v>
+      </c>
+      <c r="I97">
+        <v>3240</v>
+      </c>
+      <c r="J97" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>185</v>
+      </c>
+      <c r="B98" t="s">
+        <v>357</v>
+      </c>
+      <c r="C98" t="s">
+        <v>386</v>
+      </c>
+      <c r="D98">
+        <v>3</v>
+      </c>
+      <c r="E98" t="s">
+        <v>393</v>
+      </c>
+      <c r="F98" t="s">
+        <v>388</v>
+      </c>
+      <c r="G98" t="s">
+        <v>327</v>
+      </c>
+      <c r="H98" t="s">
+        <v>190</v>
+      </c>
+      <c r="I98">
+        <v>330</v>
+      </c>
+      <c r="J98" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>185</v>
+      </c>
+      <c r="B99" t="s">
+        <v>357</v>
+      </c>
+      <c r="C99" t="s">
+        <v>386</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99" t="s">
+        <v>394</v>
+      </c>
+      <c r="F99" t="s">
+        <v>388</v>
+      </c>
+      <c r="G99" t="s">
+        <v>327</v>
+      </c>
+      <c r="H99" t="s">
+        <v>190</v>
+      </c>
+      <c r="I99">
+        <v>440</v>
+      </c>
+      <c r="J99" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>185</v>
+      </c>
+      <c r="B100" t="s">
+        <v>357</v>
+      </c>
+      <c r="C100" t="s">
+        <v>386</v>
+      </c>
+      <c r="D100">
+        <v>7</v>
+      </c>
+      <c r="E100" t="s">
+        <v>395</v>
+      </c>
+      <c r="F100" t="s">
+        <v>388</v>
+      </c>
+      <c r="G100" t="s">
+        <v>327</v>
+      </c>
+      <c r="H100" t="s">
+        <v>190</v>
+      </c>
+      <c r="I100">
+        <v>770</v>
+      </c>
+      <c r="J100" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>185</v>
+      </c>
+      <c r="B101" t="s">
+        <v>357</v>
+      </c>
+      <c r="C101" t="s">
+        <v>386</v>
+      </c>
+      <c r="D101">
+        <v>10</v>
+      </c>
+      <c r="E101" t="s">
+        <v>396</v>
+      </c>
+      <c r="F101" t="s">
+        <v>388</v>
+      </c>
+      <c r="G101" t="s">
+        <v>327</v>
+      </c>
+      <c r="H101" t="s">
+        <v>190</v>
+      </c>
+      <c r="I101">
+        <v>1100</v>
+      </c>
+      <c r="J101" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>185</v>
+      </c>
+      <c r="B102" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" t="s">
+        <v>312</v>
+      </c>
+      <c r="D102">
+        <v>3</v>
+      </c>
+      <c r="E102" t="s">
+        <v>397</v>
+      </c>
+      <c r="F102" t="s">
+        <v>398</v>
+      </c>
+      <c r="G102" t="s">
+        <v>327</v>
+      </c>
+      <c r="H102" t="s">
+        <v>190</v>
+      </c>
+      <c r="I102">
+        <v>5400</v>
+      </c>
+      <c r="J102" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>185</v>
+      </c>
+      <c r="B103" t="s">
+        <v>399</v>
+      </c>
+      <c r="C103" t="s">
+        <v>312</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103" t="s">
+        <v>400</v>
+      </c>
+      <c r="F103" t="s">
+        <v>401</v>
+      </c>
+      <c r="G103" t="s">
+        <v>402</v>
+      </c>
+      <c r="H103" t="s">
+        <v>183</v>
+      </c>
+      <c r="I103">
+        <v>1920</v>
+      </c>
+      <c r="J103" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>185</v>
+      </c>
+      <c r="B104" t="s">
+        <v>399</v>
+      </c>
+      <c r="C104" t="s">
+        <v>312</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104" t="s">
+        <v>400</v>
+      </c>
+      <c r="F104" t="s">
+        <v>403</v>
+      </c>
+      <c r="G104" t="s">
+        <v>402</v>
+      </c>
+      <c r="H104" t="s">
+        <v>183</v>
+      </c>
+      <c r="I104">
+        <v>550</v>
+      </c>
+      <c r="J104" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" t="s">
+        <v>62</v>
+      </c>
+      <c r="C105" t="s">
+        <v>312</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105" t="s">
+        <v>404</v>
+      </c>
+      <c r="F105" t="s">
+        <v>405</v>
+      </c>
+      <c r="G105" t="s">
+        <v>406</v>
+      </c>
+      <c r="H105" t="s">
+        <v>183</v>
+      </c>
+      <c r="I105">
+        <v>780</v>
+      </c>
+      <c r="J105" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>166</v>
+      </c>
+      <c r="B106" t="s">
+        <v>167</v>
+      </c>
+      <c r="C106" t="s">
+        <v>308</v>
+      </c>
+      <c r="D106">
+        <v>6</v>
+      </c>
+      <c r="E106" t="s">
+        <v>407</v>
+      </c>
+      <c r="F106" t="s">
+        <v>408</v>
+      </c>
+      <c r="G106" t="s">
+        <v>409</v>
+      </c>
+      <c r="H106" t="s">
+        <v>410</v>
+      </c>
+      <c r="I106">
+        <v>1200</v>
+      </c>
+      <c r="J106" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>166</v>
+      </c>
+      <c r="B107" t="s">
+        <v>167</v>
+      </c>
+      <c r="C107" t="s">
+        <v>308</v>
+      </c>
+      <c r="D107">
+        <v>6</v>
+      </c>
+      <c r="E107" t="s">
+        <v>407</v>
+      </c>
+      <c r="F107" t="s">
+        <v>411</v>
+      </c>
+      <c r="G107" t="s">
+        <v>409</v>
+      </c>
+      <c r="H107" t="s">
+        <v>410</v>
+      </c>
+      <c r="I107">
+        <v>1200</v>
+      </c>
+      <c r="J107" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>166</v>
+      </c>
+      <c r="B108" t="s">
+        <v>167</v>
+      </c>
+      <c r="C108" t="s">
+        <v>308</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+      <c r="E108" t="s">
+        <v>407</v>
+      </c>
+      <c r="F108" t="s">
+        <v>412</v>
+      </c>
+      <c r="G108" t="s">
+        <v>409</v>
+      </c>
+      <c r="H108" t="s">
+        <v>410</v>
+      </c>
+      <c r="I108">
+        <v>600</v>
+      </c>
+      <c r="J108" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>166</v>
+      </c>
+      <c r="B109" t="s">
+        <v>167</v>
+      </c>
+      <c r="C109" t="s">
+        <v>308</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+      <c r="E109" t="s">
+        <v>413</v>
+      </c>
+      <c r="F109" t="s">
+        <v>414</v>
+      </c>
+      <c r="G109" t="s">
+        <v>409</v>
+      </c>
+      <c r="H109" t="s">
+        <v>410</v>
+      </c>
+      <c r="I109">
+        <v>1000</v>
+      </c>
+      <c r="J109" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>166</v>
+      </c>
+      <c r="B110" t="s">
+        <v>167</v>
+      </c>
+      <c r="C110" t="s">
+        <v>308</v>
+      </c>
+      <c r="D110">
+        <v>2</v>
+      </c>
+      <c r="E110" t="s">
+        <v>415</v>
+      </c>
+      <c r="F110" t="s">
+        <v>416</v>
+      </c>
+      <c r="G110" t="s">
+        <v>409</v>
+      </c>
+      <c r="H110" t="s">
+        <v>410</v>
+      </c>
+      <c r="I110">
+        <v>1000</v>
+      </c>
+      <c r="J110" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>221</v>
       </c>
-      <c r="I56">
-        <v>270</v>
-      </c>
-      <c r="J56" t="s">
-        <v>248</v>
-      </c>
-      <c r="K56" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>175</v>
-      </c>
-      <c r="B57" t="s">
-        <v>249</v>
-      </c>
-      <c r="C57">
+      <c r="B111" t="s">
+        <v>417</v>
+      </c>
+      <c r="C111" t="s">
+        <v>312</v>
+      </c>
+      <c r="D111">
         <v>5</v>
       </c>
-      <c r="D57">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
-        <v>250</v>
-      </c>
-      <c r="F57" t="s">
-        <v>251</v>
-      </c>
-      <c r="G57" t="s">
-        <v>252</v>
-      </c>
-      <c r="H57" t="s">
-        <v>192</v>
-      </c>
-      <c r="I57">
-        <v>450</v>
-      </c>
-      <c r="J57" t="s">
-        <v>253</v>
-      </c>
-      <c r="K57" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>175</v>
-      </c>
-      <c r="B58" t="s">
-        <v>249</v>
-      </c>
-      <c r="C58">
-        <v>5</v>
-      </c>
-      <c r="D58">
-        <v>10</v>
-      </c>
-      <c r="E58" t="s">
-        <v>250</v>
-      </c>
-      <c r="F58" t="s">
-        <v>254</v>
-      </c>
-      <c r="G58" t="s">
-        <v>252</v>
-      </c>
-      <c r="H58" t="s">
-        <v>192</v>
-      </c>
-      <c r="I58">
-        <v>500</v>
-      </c>
-      <c r="J58" t="s">
-        <v>255</v>
-      </c>
-      <c r="K58" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>175</v>
-      </c>
-      <c r="B59" t="s">
-        <v>249</v>
-      </c>
-      <c r="C59">
-        <v>5</v>
-      </c>
-      <c r="D59">
-        <v>9</v>
-      </c>
-      <c r="E59" t="s">
-        <v>256</v>
-      </c>
-      <c r="F59" t="s">
-        <v>251</v>
-      </c>
-      <c r="G59" t="s">
-        <v>252</v>
-      </c>
-      <c r="H59" t="s">
-        <v>192</v>
-      </c>
-      <c r="I59">
-        <v>450</v>
-      </c>
-      <c r="J59" t="s">
-        <v>257</v>
-      </c>
-      <c r="K59" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>175</v>
-      </c>
-      <c r="B60" t="s">
-        <v>249</v>
-      </c>
-      <c r="C60">
-        <v>5</v>
-      </c>
-      <c r="D60">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>256</v>
-      </c>
-      <c r="F60" t="s">
-        <v>254</v>
-      </c>
-      <c r="G60" t="s">
-        <v>252</v>
-      </c>
-      <c r="H60" t="s">
-        <v>192</v>
-      </c>
-      <c r="I60">
-        <v>500</v>
-      </c>
-      <c r="J60" t="s">
-        <v>258</v>
-      </c>
-      <c r="K60" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>194</v>
-      </c>
-      <c r="B61" t="s">
-        <v>259</v>
-      </c>
-      <c r="C61">
-        <v>19</v>
-      </c>
-      <c r="D61">
-        <v>50</v>
-      </c>
-      <c r="F61" t="s">
-        <v>260</v>
-      </c>
-      <c r="G61" t="s">
-        <v>261</v>
-      </c>
-      <c r="H61" t="s">
-        <v>192</v>
-      </c>
-      <c r="I61">
-        <v>2750</v>
-      </c>
-      <c r="J61" t="s">
-        <v>262</v>
-      </c>
-      <c r="K61" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>194</v>
-      </c>
-      <c r="B62" t="s">
-        <v>259</v>
-      </c>
-      <c r="C62">
-        <v>19</v>
-      </c>
-      <c r="D62">
-        <v>50</v>
-      </c>
-      <c r="F62" t="s">
-        <v>263</v>
-      </c>
-      <c r="G62" t="s">
-        <v>261</v>
-      </c>
-      <c r="H62" t="s">
-        <v>192</v>
-      </c>
-      <c r="I62">
-        <v>2750</v>
-      </c>
-      <c r="J62" t="s">
-        <v>264</v>
-      </c>
-      <c r="K62" t="s">
-        <v>49</v>
+      <c r="E111" t="s">
+        <v>418</v>
+      </c>
+      <c r="F111" t="s">
+        <v>419</v>
+      </c>
+      <c r="G111" t="s">
+        <v>420</v>
+      </c>
+      <c r="H111" t="s">
+        <v>190</v>
+      </c>
+      <c r="I111">
+        <v>315</v>
+      </c>
+      <c r="J111" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>221</v>
+      </c>
+      <c r="B112" t="s">
+        <v>417</v>
+      </c>
+      <c r="C112" t="s">
+        <v>312</v>
+      </c>
+      <c r="D112">
+        <v>12</v>
+      </c>
+      <c r="E112" t="s">
+        <v>418</v>
+      </c>
+      <c r="F112" t="s">
+        <v>421</v>
+      </c>
+      <c r="G112" t="s">
+        <v>420</v>
+      </c>
+      <c r="H112" t="s">
+        <v>190</v>
+      </c>
+      <c r="I112">
+        <v>720</v>
+      </c>
+      <c r="J112" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>221</v>
+      </c>
+      <c r="B113" t="s">
+        <v>417</v>
+      </c>
+      <c r="C113" t="s">
+        <v>312</v>
+      </c>
+      <c r="D113">
+        <v>3</v>
+      </c>
+      <c r="E113" t="s">
+        <v>418</v>
+      </c>
+      <c r="F113" t="s">
+        <v>422</v>
+      </c>
+      <c r="G113" t="s">
+        <v>420</v>
+      </c>
+      <c r="H113" t="s">
+        <v>190</v>
+      </c>
+      <c r="I113">
+        <v>360</v>
+      </c>
+      <c r="J113" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>185</v>
+      </c>
+      <c r="B114" t="s">
+        <v>123</v>
+      </c>
+      <c r="C114" t="s">
+        <v>312</v>
+      </c>
+      <c r="D114">
+        <v>30</v>
+      </c>
+      <c r="E114" t="s">
+        <v>423</v>
+      </c>
+      <c r="F114" t="s">
+        <v>424</v>
+      </c>
+      <c r="G114" t="s">
+        <v>189</v>
+      </c>
+      <c r="H114" t="s">
+        <v>190</v>
+      </c>
+      <c r="I114">
+        <v>2640</v>
+      </c>
+      <c r="J114" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>166</v>
+      </c>
+      <c r="B115" t="s">
+        <v>135</v>
+      </c>
+      <c r="C115" t="s">
+        <v>337</v>
+      </c>
+      <c r="D115">
+        <v>4</v>
+      </c>
+      <c r="E115" t="s">
+        <v>425</v>
+      </c>
+      <c r="F115" t="s">
+        <v>426</v>
+      </c>
+      <c r="G115" t="s">
+        <v>427</v>
+      </c>
+      <c r="H115" t="s">
+        <v>183</v>
+      </c>
+      <c r="I115">
+        <v>2500</v>
+      </c>
+      <c r="J115" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24896DEB-BFB8-461E-9BF2-964517D70F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F88B1F2-6127-45A5-B7A5-75F7513F505D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="196">
   <si>
     <t>Responsável</t>
   </si>
@@ -222,6 +222,405 @@
   </si>
   <si>
     <t>LP-060453</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>685551</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>4730502260</t>
+  </si>
+  <si>
+    <t>Pino de arraste 7mm</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>CtP/TEF11</t>
+  </si>
+  <si>
+    <t>LP-060480</t>
+  </si>
+  <si>
+    <t>685552</t>
+  </si>
+  <si>
+    <t>4710101287</t>
+  </si>
+  <si>
+    <t>Jogo de garra</t>
+  </si>
+  <si>
+    <t>LP-060481</t>
+  </si>
+  <si>
+    <t>685700</t>
+  </si>
+  <si>
+    <t>4710900938</t>
+  </si>
+  <si>
+    <t>Posição 1</t>
+  </si>
+  <si>
+    <t>LP-060482</t>
+  </si>
+  <si>
+    <t>4711400654</t>
+  </si>
+  <si>
+    <t>Garra</t>
+  </si>
+  <si>
+    <t>LP-060483</t>
+  </si>
+  <si>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>685557</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>4711301144</t>
+  </si>
+  <si>
+    <t>Pino montadora</t>
+  </si>
+  <si>
+    <t>TKC1CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS21-BR</t>
+  </si>
+  <si>
+    <t>LP-060486</t>
+  </si>
+  <si>
+    <t>4711301145</t>
+  </si>
+  <si>
+    <t>LP-060487</t>
+  </si>
+  <si>
+    <t>4711301146</t>
+  </si>
+  <si>
+    <t>LP-060488</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>685615</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>4716404427-0002</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-060489</t>
+  </si>
+  <si>
+    <t>685485</t>
+  </si>
+  <si>
+    <t>4711202468</t>
+  </si>
+  <si>
+    <t>IP 685485 Suporte de alimentação Zema</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>LP-060491</t>
+  </si>
+  <si>
+    <t>685531</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4710100830</t>
+  </si>
+  <si>
+    <t>Confecção dispositivo anel trava DHK</t>
+  </si>
+  <si>
+    <t>MMA5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW11-C</t>
+  </si>
+  <si>
+    <t>LP-060492</t>
+  </si>
+  <si>
+    <t>4710100394</t>
+  </si>
+  <si>
+    <t>IP-685485-Brunidora preparar.CIL P3.⌀10</t>
+  </si>
+  <si>
+    <t>LP-060493</t>
+  </si>
+  <si>
+    <t>685487</t>
+  </si>
+  <si>
+    <t>4729401824</t>
+  </si>
+  <si>
+    <t>IP-685487 Bucha de recolhimento Ø9,5 A</t>
+  </si>
+  <si>
+    <t>LP-060494</t>
+  </si>
+  <si>
+    <t>685434</t>
+  </si>
+  <si>
+    <t>4716506412</t>
+  </si>
+  <si>
+    <t>Novo - série 0174</t>
+  </si>
+  <si>
+    <t>LP-060495</t>
+  </si>
+  <si>
+    <t>685412</t>
+  </si>
+  <si>
+    <t>4716406434</t>
+  </si>
+  <si>
+    <t>Novo - série 0002</t>
+  </si>
+  <si>
+    <t>LP-060496</t>
+  </si>
+  <si>
+    <t>4716406393</t>
+  </si>
+  <si>
+    <t>Novo - série 0003</t>
+  </si>
+  <si>
+    <t>LP-060497</t>
+  </si>
+  <si>
+    <t>4716509013</t>
+  </si>
+  <si>
+    <t>Novo - série 0009</t>
+  </si>
+  <si>
+    <t>LP-060498</t>
+  </si>
+  <si>
+    <t>Renato Meira</t>
+  </si>
+  <si>
+    <t>685050</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>4729111568</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO MIKRON</t>
+  </si>
+  <si>
+    <t>JULIANA MELO</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>LP-060499</t>
+  </si>
+  <si>
+    <t>685411</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>4711201792</t>
+  </si>
+  <si>
+    <t>Alterar desenho do pino soprador - Nomy</t>
+  </si>
+  <si>
+    <t>GEOVANE</t>
+  </si>
+  <si>
+    <t>LP-060500</t>
+  </si>
+  <si>
+    <t>685433</t>
+  </si>
+  <si>
+    <t>4716507926-0011</t>
+  </si>
+  <si>
+    <t>LY - conserto</t>
+  </si>
+  <si>
+    <t>LP-060501</t>
+  </si>
+  <si>
+    <t>4716507912-0022</t>
+  </si>
+  <si>
+    <t>LP-060502</t>
+  </si>
+  <si>
+    <t>4716507925-0011</t>
+  </si>
+  <si>
+    <t>LP-060503</t>
+  </si>
+  <si>
+    <t>4716507925-0007</t>
+  </si>
+  <si>
+    <t>LP-060504</t>
+  </si>
+  <si>
+    <t>4716507925-0006</t>
+  </si>
+  <si>
+    <t>LP-060505</t>
+  </si>
+  <si>
+    <t>4716507926-0009</t>
+  </si>
+  <si>
+    <t>LP-060506</t>
+  </si>
+  <si>
+    <t>4716508124</t>
+  </si>
+  <si>
+    <t>Novos - Control System</t>
+  </si>
+  <si>
+    <t>LP-060507</t>
+  </si>
+  <si>
+    <t>4716508123</t>
+  </si>
+  <si>
+    <t>LP-060508</t>
+  </si>
+  <si>
+    <t>Rafael Lima</t>
+  </si>
+  <si>
+    <t>685134</t>
+  </si>
+  <si>
+    <t>4717600158</t>
+  </si>
+  <si>
+    <t>ARRASTADOR IMPRESSO EM 3D (PARA TESTE)</t>
+  </si>
+  <si>
+    <t>R. CHLAD</t>
+  </si>
+  <si>
+    <t>CtP/MFE31</t>
+  </si>
+  <si>
+    <t>LP-060512</t>
+  </si>
+  <si>
+    <t>4711500240</t>
+  </si>
+  <si>
+    <t>685552 Manutenção placa SPINNER</t>
+  </si>
+  <si>
+    <t>MARCIO</t>
+  </si>
+  <si>
+    <t>LP-060513</t>
+  </si>
+  <si>
+    <t>4710800241</t>
+  </si>
+  <si>
+    <t>Contra ponto</t>
+  </si>
+  <si>
+    <t>LP-060514</t>
+  </si>
+  <si>
+    <t>685606</t>
+  </si>
+  <si>
+    <t>4729110426</t>
+  </si>
+  <si>
+    <t>Bico vacuo st 30 com furos</t>
+  </si>
+  <si>
+    <t>ZAK2CT</t>
+  </si>
+  <si>
+    <t>LP-060515</t>
+  </si>
+  <si>
+    <t>4710900857</t>
+  </si>
+  <si>
+    <t>Bit parafuso de tensão CRI</t>
+  </si>
+  <si>
+    <t>LP-060516</t>
+  </si>
+  <si>
+    <t>685401</t>
+  </si>
+  <si>
+    <t>4729107174</t>
+  </si>
+  <si>
+    <t>Porca sextavada ECM</t>
+  </si>
+  <si>
+    <t>LP-060520</t>
+  </si>
+  <si>
+    <t>4729111430</t>
+  </si>
+  <si>
+    <t>DU 685411 POS 2 &amp; 3 do dedo marpos HTT</t>
+  </si>
+  <si>
+    <t>LP-060521</t>
   </si>
 </sst>
 </file>
@@ -561,23 +960,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -612,442 +1020,1468 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2">
+        <v>1200</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="N2" t="s">
         <v>12</v>
       </c>
-      <c r="C2">
+      <c r="O2">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="R2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="S2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="T2" t="s">
         <v>16</v>
       </c>
-      <c r="I2">
+      <c r="U2">
         <v>36000</v>
       </c>
-      <c r="J2" t="s">
+      <c r="V2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3">
+        <v>8000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="O3">
         <v>6</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="R3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="S3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
+      <c r="T3" t="s">
         <v>16</v>
       </c>
-      <c r="I3">
+      <c r="U3">
         <v>0.01</v>
       </c>
-      <c r="J3" t="s">
+      <c r="V3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4">
+        <v>5500</v>
+      </c>
+      <c r="J4" t="s">
+        <v>78</v>
+      </c>
+      <c r="M4" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
+      <c r="O4">
         <v>6</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="R4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="S4" t="s">
         <v>15</v>
       </c>
-      <c r="H4" t="s">
+      <c r="T4" t="s">
         <v>16</v>
       </c>
-      <c r="I4">
+      <c r="U4">
         <v>0.01</v>
       </c>
-      <c r="J4" t="s">
+      <c r="V4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5">
+        <v>7040</v>
+      </c>
+      <c r="J5" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
+      <c r="O5">
         <v>6</v>
       </c>
-      <c r="D5">
+      <c r="P5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
+      <c r="Q5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="R5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
+      <c r="S5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
+      <c r="T5" t="s">
         <v>16</v>
       </c>
-      <c r="I5">
+      <c r="U5">
         <v>0.01</v>
       </c>
-      <c r="J5" t="s">
+      <c r="V5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" t="s">
         <v>11</v>
       </c>
-      <c r="C6">
+      <c r="O6">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="P6">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
+      <c r="Q6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" t="s">
+      <c r="R6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
+      <c r="S6" t="s">
         <v>15</v>
       </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
         <v>16</v>
       </c>
-      <c r="I6">
+      <c r="U6">
         <v>0.01</v>
       </c>
-      <c r="J6" t="s">
+      <c r="V6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" t="s">
         <v>11</v>
       </c>
-      <c r="C7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="P7">
         <v>3</v>
       </c>
-      <c r="E7" t="s">
+      <c r="Q7" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
+      <c r="R7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" t="s">
+      <c r="S7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" t="s">
+      <c r="T7" t="s">
         <v>16</v>
       </c>
-      <c r="I7">
+      <c r="U7">
         <v>0.01</v>
       </c>
-      <c r="J7" t="s">
+      <c r="V7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="O8">
         <v>6</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
         <v>33</v>
       </c>
-      <c r="F8" t="s">
+      <c r="R8" t="s">
         <v>34</v>
       </c>
-      <c r="G8" t="s">
+      <c r="S8" t="s">
         <v>15</v>
       </c>
-      <c r="H8" t="s">
+      <c r="T8" t="s">
         <v>16</v>
       </c>
-      <c r="I8">
+      <c r="U8">
         <v>0.01</v>
       </c>
-      <c r="J8" t="s">
+      <c r="V8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>101</v>
+      </c>
+      <c r="M9" t="s">
         <v>11</v>
       </c>
-      <c r="C9">
+      <c r="O9">
         <v>6</v>
       </c>
-      <c r="D9">
+      <c r="P9">
         <v>3</v>
       </c>
-      <c r="E9" t="s">
+      <c r="Q9" t="s">
         <v>36</v>
       </c>
-      <c r="F9" t="s">
+      <c r="R9" t="s">
         <v>37</v>
       </c>
-      <c r="G9" t="s">
+      <c r="S9" t="s">
         <v>15</v>
       </c>
-      <c r="H9" t="s">
+      <c r="T9" t="s">
         <v>16</v>
       </c>
-      <c r="I9">
+      <c r="U9">
         <v>0.01</v>
       </c>
-      <c r="J9" t="s">
+      <c r="V9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10">
+        <v>12000</v>
+      </c>
+      <c r="J10" t="s">
+        <v>106</v>
+      </c>
+      <c r="M10" t="s">
         <v>11</v>
       </c>
-      <c r="C10">
+      <c r="O10">
         <v>6</v>
       </c>
-      <c r="D10">
+      <c r="P10">
         <v>3</v>
       </c>
-      <c r="E10" t="s">
+      <c r="Q10" t="s">
         <v>39</v>
       </c>
-      <c r="F10" t="s">
+      <c r="R10" t="s">
         <v>40</v>
       </c>
-      <c r="G10" t="s">
+      <c r="S10" t="s">
         <v>15</v>
       </c>
-      <c r="H10" t="s">
+      <c r="T10" t="s">
         <v>16</v>
       </c>
-      <c r="I10">
+      <c r="U10">
         <v>0.01</v>
       </c>
-      <c r="J10" t="s">
+      <c r="V10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11">
+        <v>2000</v>
+      </c>
+      <c r="J11" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11" t="s">
         <v>11</v>
       </c>
-      <c r="C11">
+      <c r="O11">
         <v>6</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="s">
         <v>42</v>
       </c>
-      <c r="F11" t="s">
+      <c r="R11" t="s">
         <v>43</v>
       </c>
-      <c r="G11" t="s">
+      <c r="S11" t="s">
         <v>15</v>
       </c>
-      <c r="H11" t="s">
+      <c r="T11" t="s">
         <v>16</v>
       </c>
-      <c r="I11">
+      <c r="U11">
         <v>0.01</v>
       </c>
-      <c r="J11" t="s">
+      <c r="V11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12">
+        <v>4800</v>
+      </c>
+      <c r="J12" t="s">
+        <v>115</v>
+      </c>
+      <c r="M12" t="s">
         <v>11</v>
       </c>
-      <c r="C12">
+      <c r="O12">
         <v>6</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
         <v>45</v>
       </c>
-      <c r="F12" t="s">
+      <c r="R12" t="s">
         <v>46</v>
       </c>
-      <c r="G12" t="s">
+      <c r="S12" t="s">
         <v>15</v>
       </c>
-      <c r="H12" t="s">
+      <c r="T12" t="s">
         <v>16</v>
       </c>
-      <c r="I12">
+      <c r="U12">
         <v>0.01</v>
       </c>
-      <c r="J12" t="s">
+      <c r="V12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13">
+        <v>2300</v>
+      </c>
+      <c r="J13" t="s">
+        <v>119</v>
+      </c>
+      <c r="M13" t="s">
         <v>11</v>
       </c>
-      <c r="C13">
+      <c r="O13">
         <v>6</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="s">
         <v>48</v>
       </c>
-      <c r="F13" t="s">
+      <c r="R13" t="s">
         <v>49</v>
       </c>
-      <c r="G13" t="s">
+      <c r="S13" t="s">
         <v>15</v>
       </c>
-      <c r="H13" t="s">
+      <c r="T13" t="s">
         <v>16</v>
       </c>
-      <c r="I13">
+      <c r="U13">
         <v>0.01</v>
       </c>
-      <c r="J13" t="s">
+      <c r="V13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>4000</v>
+      </c>
+      <c r="J14" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14" t="s">
         <v>11</v>
       </c>
-      <c r="C14">
+      <c r="O14">
         <v>6</v>
       </c>
-      <c r="D14">
+      <c r="P14">
         <v>2</v>
       </c>
-      <c r="E14" t="s">
+      <c r="Q14" t="s">
         <v>51</v>
       </c>
-      <c r="F14" t="s">
+      <c r="R14" t="s">
         <v>52</v>
       </c>
-      <c r="G14" t="s">
+      <c r="S14" t="s">
         <v>15</v>
       </c>
-      <c r="H14" t="s">
+      <c r="T14" t="s">
         <v>16</v>
       </c>
-      <c r="I14">
+      <c r="U14">
         <v>0.01</v>
       </c>
-      <c r="J14" t="s">
+      <c r="V14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15">
+        <v>4500</v>
+      </c>
+      <c r="J15" t="s">
+        <v>127</v>
+      </c>
+      <c r="M15" t="s">
         <v>11</v>
       </c>
-      <c r="C15">
+      <c r="O15">
         <v>6</v>
       </c>
-      <c r="D15">
+      <c r="P15">
         <v>4</v>
       </c>
-      <c r="E15" t="s">
+      <c r="Q15" t="s">
         <v>54</v>
       </c>
-      <c r="F15" t="s">
+      <c r="R15" t="s">
         <v>55</v>
       </c>
-      <c r="G15" t="s">
+      <c r="S15" t="s">
         <v>15</v>
       </c>
-      <c r="H15" t="s">
+      <c r="T15" t="s">
         <v>16</v>
       </c>
-      <c r="I15">
+      <c r="U15">
         <v>0.01</v>
       </c>
-      <c r="J15" t="s">
+      <c r="V15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <v>4500</v>
+      </c>
+      <c r="J16" t="s">
+        <v>130</v>
+      </c>
+      <c r="M16" t="s">
         <v>57</v>
       </c>
-      <c r="B16" t="s">
+      <c r="N16" t="s">
         <v>58</v>
       </c>
-      <c r="C16">
+      <c r="O16">
         <v>5</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="R16" t="s">
         <v>59</v>
       </c>
-      <c r="G16" t="s">
+      <c r="S16" t="s">
         <v>60</v>
       </c>
-      <c r="H16" t="s">
+      <c r="T16" t="s">
         <v>61</v>
       </c>
-      <c r="I16">
+      <c r="U16">
         <v>2000</v>
       </c>
-      <c r="J16" t="s">
+      <c r="V16" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>3000</v>
+      </c>
+      <c r="J17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18" t="s">
+        <v>139</v>
+      </c>
+      <c r="H18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18">
+        <v>480</v>
+      </c>
+      <c r="J18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19">
+        <v>480</v>
+      </c>
+      <c r="J19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <v>600</v>
+      </c>
+      <c r="J20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" t="s">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>600</v>
+      </c>
+      <c r="J21" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" t="s">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>600</v>
+      </c>
+      <c r="J22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>600</v>
+      </c>
+      <c r="J23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>600</v>
+      </c>
+      <c r="J24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" t="s">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>600</v>
+      </c>
+      <c r="J25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26">
+        <v>75</v>
+      </c>
+      <c r="E26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" t="s">
+        <v>163</v>
+      </c>
+      <c r="G26" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>1850</v>
+      </c>
+      <c r="J26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27">
+        <v>75</v>
+      </c>
+      <c r="E27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" t="s">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>1850</v>
+      </c>
+      <c r="J27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28">
+        <v>360</v>
+      </c>
+      <c r="J28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" t="s">
+        <v>176</v>
+      </c>
+      <c r="H29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29">
+        <v>3000</v>
+      </c>
+      <c r="J29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30" t="s">
+        <v>179</v>
+      </c>
+      <c r="G30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30">
+        <v>660</v>
+      </c>
+      <c r="J30" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" t="s">
+        <v>184</v>
+      </c>
+      <c r="H31" t="s">
+        <v>140</v>
+      </c>
+      <c r="I31">
+        <v>2240</v>
+      </c>
+      <c r="J31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>181</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" t="s">
+        <v>140</v>
+      </c>
+      <c r="I32">
+        <v>2600</v>
+      </c>
+      <c r="J32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" t="s">
+        <v>191</v>
+      </c>
+      <c r="G33" t="s">
+        <v>139</v>
+      </c>
+      <c r="H33" t="s">
+        <v>140</v>
+      </c>
+      <c r="I33">
+        <v>8000</v>
+      </c>
+      <c r="J33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G34" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" t="s">
+        <v>69</v>
+      </c>
+      <c r="I34">
+        <v>3000</v>
+      </c>
+      <c r="J34" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67D1983-48B2-4BEA-939C-E54929A3D284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9459306B-780C-4078-8989-F2BA3F716760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
   <si>
     <t>Responsável</t>
   </si>
@@ -55,25 +68,175 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Cadastrado</t>
-  </si>
-  <si>
-    <t>Thais Fischer</t>
-  </si>
-  <si>
-    <t>Dispositivo prensagem para UPCRS</t>
-  </si>
-  <si>
-    <t>ROB2CT</t>
-  </si>
-  <si>
-    <t>PS-DC/ENS1-LA</t>
-  </si>
-  <si>
-    <t>LP-060453</t>
-  </si>
-  <si>
-    <t>BM-00108513_008_00000014</t>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>685411</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>GARRA STUDER</t>
+  </si>
+  <si>
+    <t>Garra Studer</t>
+  </si>
+  <si>
+    <t>JULIANA MELO</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>LP-060523</t>
+  </si>
+  <si>
+    <t>685485</t>
+  </si>
+  <si>
+    <t>4710100394</t>
+  </si>
+  <si>
+    <t>IP-685485-Brunidora d preparar.CIL P3⌀10</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>CtP/TEF11</t>
+  </si>
+  <si>
+    <t>LP-060524</t>
+  </si>
+  <si>
+    <t>685907</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>3418260604</t>
+  </si>
+  <si>
+    <t>Retificar Sol Pistão LE</t>
+  </si>
+  <si>
+    <t>COR4CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE12</t>
+  </si>
+  <si>
+    <t>LP-060525</t>
+  </si>
+  <si>
+    <t>Rafael Lima</t>
+  </si>
+  <si>
+    <t>685172</t>
+  </si>
+  <si>
+    <t>DESENHO EM ANEXO</t>
+  </si>
+  <si>
+    <t>CONFECÇÃO DE GARRA PARA STUDER</t>
+  </si>
+  <si>
+    <t>CARLOS REIS</t>
+  </si>
+  <si>
+    <t>LP-060526</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>685482</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>4716511880</t>
+  </si>
+  <si>
+    <t>Novos- série 0001 e 0002</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-060527</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SUPORTE LCMV</t>
+  </si>
+  <si>
+    <t>LP-060528</t>
+  </si>
+  <si>
+    <t>4716404177</t>
+  </si>
+  <si>
+    <t>Novo-Série 0006</t>
+  </si>
+  <si>
+    <t>LP-060529</t>
+  </si>
+  <si>
+    <t>4716406477</t>
+  </si>
+  <si>
+    <t>Novo - série 0003</t>
+  </si>
+  <si>
+    <t>LP-060530</t>
+  </si>
+  <si>
+    <t>4711401373</t>
+  </si>
+  <si>
+    <t>CASTANHA UVA</t>
+  </si>
+  <si>
+    <t>LP-060531</t>
+  </si>
+  <si>
+    <t>685551</t>
+  </si>
+  <si>
+    <t>4716403840</t>
+  </si>
+  <si>
+    <t>posição 13.</t>
+  </si>
+  <si>
+    <t>LP-060532</t>
+  </si>
+  <si>
+    <t>Edson Bento</t>
+  </si>
+  <si>
+    <t>685376</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>RETRABALHO PLACA</t>
+  </si>
+  <si>
+    <t>SOL5CT</t>
+  </si>
+  <si>
+    <t>LP-060533</t>
   </si>
 </sst>
 </file>
@@ -413,20 +576,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -466,34 +629,354 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
+      <c r="I2">
+        <v>1500</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>6000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>400</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4">
+        <v>10000</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>225</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6">
+        <v>2200</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>270</v>
+      </c>
+      <c r="J7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8">
+        <v>1200</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9">
+        <v>5500</v>
+      </c>
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>2000</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10">
+        <v>225</v>
+      </c>
+      <c r="J10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9459306B-780C-4078-8989-F2BA3F716760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF98901-E2E1-4A89-8C84-8F7843D602DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="143">
   <si>
     <t>Responsável</t>
   </si>
@@ -71,12 +71,6 @@
     <t>Marcelo Simoes</t>
   </si>
   <si>
-    <t>685411</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>GARRA STUDER</t>
   </si>
   <si>
@@ -92,12 +86,6 @@
     <t>LP-060523</t>
   </si>
   <si>
-    <t>685485</t>
-  </si>
-  <si>
-    <t>4710100394</t>
-  </si>
-  <si>
     <t>IP-685485-Brunidora d preparar.CIL P3⌀10</t>
   </si>
   <si>
@@ -110,15 +98,6 @@
     <t>LP-060524</t>
   </si>
   <si>
-    <t>685907</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>3418260604</t>
-  </si>
-  <si>
     <t>Retificar Sol Pistão LE</t>
   </si>
   <si>
@@ -134,9 +113,6 @@
     <t>Rafael Lima</t>
   </si>
   <si>
-    <t>685172</t>
-  </si>
-  <si>
     <t>DESENHO EM ANEXO</t>
   </si>
   <si>
@@ -152,15 +128,6 @@
     <t>Rodrigo Melo</t>
   </si>
   <si>
-    <t>685482</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>4716511880</t>
-  </si>
-  <si>
     <t>Novos- série 0001 e 0002</t>
   </si>
   <si>
@@ -182,39 +149,24 @@
     <t>LP-060528</t>
   </si>
   <si>
-    <t>4716404177</t>
-  </si>
-  <si>
     <t>Novo-Série 0006</t>
   </si>
   <si>
     <t>LP-060529</t>
   </si>
   <si>
-    <t>4716406477</t>
-  </si>
-  <si>
     <t>Novo - série 0003</t>
   </si>
   <si>
     <t>LP-060530</t>
   </si>
   <si>
-    <t>4711401373</t>
-  </si>
-  <si>
     <t>CASTANHA UVA</t>
   </si>
   <si>
     <t>LP-060531</t>
   </si>
   <si>
-    <t>685551</t>
-  </si>
-  <si>
-    <t>4716403840</t>
-  </si>
-  <si>
     <t>posição 13.</t>
   </si>
   <si>
@@ -224,9 +176,6 @@
     <t>Edson Bento</t>
   </si>
   <si>
-    <t>685376</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
@@ -237,6 +186,282 @@
   </si>
   <si>
     <t>LP-060533</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>DISPOSITIVO PICK UP</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>LP-054419</t>
+  </si>
+  <si>
+    <t>Novo -Série 0002</t>
+  </si>
+  <si>
+    <t>PS/QMM61-CtP</t>
+  </si>
+  <si>
+    <t>LP-054574</t>
+  </si>
+  <si>
+    <t>IP 685485 - Elemento A 3D.</t>
+  </si>
+  <si>
+    <t>MILENY MAIA</t>
+  </si>
+  <si>
+    <t>CtP/MFW11-D</t>
+  </si>
+  <si>
+    <t>LP-054634</t>
+  </si>
+  <si>
+    <t>IP 685484 - Elemento A 3D.</t>
+  </si>
+  <si>
+    <t>LP-054635</t>
+  </si>
+  <si>
+    <t>IP 685010- Elemento A 3D.</t>
+  </si>
+  <si>
+    <t>LP-054636</t>
+  </si>
+  <si>
+    <t>BM-00040171_001_00000020</t>
+  </si>
+  <si>
+    <t>0414Y00338-01</t>
+  </si>
+  <si>
+    <t>Eixo performance</t>
+  </si>
+  <si>
+    <t>FOM2CT</t>
+  </si>
+  <si>
+    <t>CtP/ETS</t>
+  </si>
+  <si>
+    <t>LP-055847</t>
+  </si>
+  <si>
+    <t>0414Y10131-01</t>
+  </si>
+  <si>
+    <t>Eixo durabilidade</t>
+  </si>
+  <si>
+    <t>LP-055848</t>
+  </si>
+  <si>
+    <t>0414Y10132-01</t>
+  </si>
+  <si>
+    <t>Suporte roda fonica</t>
+  </si>
+  <si>
+    <t>LP-055849</t>
+  </si>
+  <si>
+    <t>0414Y10133-01</t>
+  </si>
+  <si>
+    <t>Roda fonica</t>
+  </si>
+  <si>
+    <t>LP-055850</t>
+  </si>
+  <si>
+    <t>0414Y10134-01</t>
+  </si>
+  <si>
+    <t>Sincrona</t>
+  </si>
+  <si>
+    <t>LP-055851</t>
+  </si>
+  <si>
+    <t>Adpt UCV Calço</t>
+  </si>
+  <si>
+    <t>LP-055852</t>
+  </si>
+  <si>
+    <t>Suporte sensor roda fonica</t>
+  </si>
+  <si>
+    <t>LP-055853</t>
+  </si>
+  <si>
+    <t>retrabalo suporte sensor</t>
+  </si>
+  <si>
+    <t>LP-055854</t>
+  </si>
+  <si>
+    <t>I68500075976</t>
+  </si>
+  <si>
+    <t>N.A</t>
+  </si>
+  <si>
+    <t>F000.UC0.0NU-04 (ELEMENTO CURTO)</t>
+  </si>
+  <si>
+    <t>PS-DC/ENP1-LA</t>
+  </si>
+  <si>
+    <t>LP-055855</t>
+  </si>
+  <si>
+    <t>F000.UC0.0NU-04 (ELEMENTO LONGO)</t>
+  </si>
+  <si>
+    <t>LP-055856</t>
+  </si>
+  <si>
+    <t>4716406392-0001</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>LP-056120</t>
+  </si>
+  <si>
+    <t>4716406392-0003</t>
+  </si>
+  <si>
+    <t>LP-056504</t>
+  </si>
+  <si>
+    <t>Dispositivo de apoio pistão</t>
+  </si>
+  <si>
+    <t>SAL5CT</t>
+  </si>
+  <si>
+    <t>LP-057826</t>
+  </si>
+  <si>
+    <t>Novo - serie 0124</t>
+  </si>
+  <si>
+    <t>LP-057926</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>Pino REMAN</t>
+  </si>
+  <si>
+    <t>LP-058034</t>
+  </si>
+  <si>
+    <t>4316400030-0394</t>
+  </si>
+  <si>
+    <t>Base - conserto</t>
+  </si>
+  <si>
+    <t>LP-058097</t>
+  </si>
+  <si>
+    <t>IP 685484 Contra ponto emparelhamento P</t>
+  </si>
+  <si>
+    <t>LP-058101</t>
+  </si>
+  <si>
+    <t>IP 685484 Rebolo borazon Pistão P</t>
+  </si>
+  <si>
+    <t>LP-058110</t>
+  </si>
+  <si>
+    <t>IP 685481 Chapa de alimentação válvula</t>
+  </si>
+  <si>
+    <t>LP-058117</t>
+  </si>
+  <si>
+    <t>4312400046-0295</t>
+  </si>
+  <si>
+    <t>LP-058127</t>
+  </si>
+  <si>
+    <t>Parafuso da Garra</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>LP-058137</t>
+  </si>
+  <si>
+    <t>4729111967/POS6</t>
+  </si>
+  <si>
+    <t>Dispo Giro DMAX</t>
+  </si>
+  <si>
+    <t>LP-058161</t>
+  </si>
+  <si>
+    <t>4716507930-0038</t>
+  </si>
+  <si>
+    <t>Conex</t>
+  </si>
+  <si>
+    <t>LP-058237</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Retrabalho castanha Hommel</t>
+  </si>
+  <si>
+    <t>VIM6CT</t>
+  </si>
+  <si>
+    <t>LP-060537</t>
+  </si>
+  <si>
+    <t>Retrabalho castanhas Twinner</t>
+  </si>
+  <si>
+    <t>HENRIQUE O.</t>
+  </si>
+  <si>
+    <t>CtP/MFE31</t>
+  </si>
+  <si>
+    <t>LP-060538</t>
+  </si>
+  <si>
+    <t>685552 MANUTENÇÃO PLACA SPINNER</t>
+  </si>
+  <si>
+    <t>MARCIO</t>
+  </si>
+  <si>
+    <t>LP-060539</t>
+  </si>
+  <si>
+    <t>LP-060540</t>
+  </si>
+  <si>
+    <t>LP-060541</t>
   </si>
 </sst>
 </file>
@@ -272,8 +497,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,15 +802,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -629,354 +855,1410 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="B2">
+        <v>685401</v>
+      </c>
+      <c r="C2">
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>685015</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4716600056</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+      <c r="B4">
+        <v>685485</v>
+      </c>
+      <c r="C4">
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>685010</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>225</v>
+        <v>2500</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>685010</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I6">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
+        <v>66</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="I7">
-        <v>270</v>
+        <v>30000</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
+        <v>66</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I8">
-        <v>1200</v>
+        <v>30000</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
+        <v>66</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I9">
-        <v>5500</v>
+        <v>1500</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
+        <v>66</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="I10">
-        <v>225</v>
+        <v>2500</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
+        <v>66</v>
+      </c>
+      <c r="C11">
+        <v>17</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I11">
         <v>1000</v>
       </c>
       <c r="J11" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12">
+        <v>500</v>
+      </c>
+      <c r="J12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13">
+        <v>800</v>
+      </c>
+      <c r="J13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14">
+        <v>800</v>
+      </c>
+      <c r="J14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15">
+        <v>10000</v>
+      </c>
+      <c r="J15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16">
+        <v>40000</v>
+      </c>
+      <c r="J16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17">
+        <v>685616</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17">
+        <v>500</v>
+      </c>
+      <c r="J17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18">
+        <v>685616</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18">
+        <v>500</v>
+      </c>
+      <c r="J18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19">
+        <v>685070</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19">
+        <v>300</v>
+      </c>
+      <c r="J19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>685608</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>4713400041</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20">
+        <v>4000</v>
+      </c>
+      <c r="J20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21">
+        <v>685555</v>
+      </c>
+      <c r="C21">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>4728602393</v>
+      </c>
+      <c r="F21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21">
+        <v>2750</v>
+      </c>
+      <c r="J21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22">
+        <v>685481</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22">
+        <v>400</v>
+      </c>
+      <c r="J22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23">
+        <v>685484</v>
+      </c>
+      <c r="C23">
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>4310800263</v>
+      </c>
+      <c r="F23" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23">
+        <v>1980</v>
+      </c>
+      <c r="J23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24">
+        <v>685484</v>
+      </c>
+      <c r="C24">
+        <v>37</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>4719270019</v>
+      </c>
+      <c r="F24" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24">
+        <v>110</v>
+      </c>
+      <c r="J24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25">
+        <v>685481</v>
+      </c>
+      <c r="C25">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>4729108742</v>
+      </c>
+      <c r="F25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25">
+        <v>840</v>
+      </c>
+      <c r="J25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26">
+        <v>685541</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26">
+        <v>400</v>
+      </c>
+      <c r="J26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27">
+        <v>685615</v>
+      </c>
+      <c r="C27">
+        <v>19</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>4711201655</v>
+      </c>
+      <c r="F27" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27">
+        <v>3900</v>
+      </c>
+      <c r="J27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>685605</v>
+      </c>
+      <c r="C28">
+        <v>19</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28">
+        <v>8000</v>
+      </c>
+      <c r="J28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>685434</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29">
+        <v>400</v>
+      </c>
+      <c r="J29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>685411</v>
+      </c>
+      <c r="C30">
+        <v>19</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30">
+        <v>1500</v>
+      </c>
+      <c r="J30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>685485</v>
+      </c>
+      <c r="C31">
+        <v>19</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>4710100394</v>
+      </c>
+      <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31">
+        <v>6000</v>
+      </c>
+      <c r="J31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>685907</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>3418260604</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32">
+        <v>10000</v>
+      </c>
+      <c r="J32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33">
+        <v>685172</v>
+      </c>
+      <c r="C33">
+        <v>19</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
         <v>26</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12">
+      <c r="F33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33">
+        <v>225</v>
+      </c>
+      <c r="J33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34">
+        <v>685482</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>4716511880</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34">
+        <v>2200</v>
+      </c>
+      <c r="J34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35">
+        <v>685172</v>
+      </c>
+      <c r="C35">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35">
+        <v>270</v>
+      </c>
+      <c r="J35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36">
+        <v>685485</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>4716404177</v>
+      </c>
+      <c r="F36" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36">
+        <v>1200</v>
+      </c>
+      <c r="J36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37">
+        <v>685485</v>
+      </c>
+      <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>4716406477</v>
+      </c>
+      <c r="F37" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" t="s">
+        <v>33</v>
+      </c>
+      <c r="I37">
+        <v>5500</v>
+      </c>
+      <c r="J37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38">
+        <v>685172</v>
+      </c>
+      <c r="C38">
+        <v>19</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>4711401373</v>
+      </c>
+      <c r="F38" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38">
+        <v>225</v>
+      </c>
+      <c r="J38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39">
+        <v>685551</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>4716403840</v>
+      </c>
+      <c r="F39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39">
         <v>1000</v>
       </c>
-      <c r="J12" t="s">
-        <v>67</v>
+      <c r="J39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
+        <v>685376</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40" t="s">
+        <v>48</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>685401</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" t="s">
+        <v>132</v>
+      </c>
+      <c r="H41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41">
+        <v>500</v>
+      </c>
+      <c r="J41" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42">
+        <v>685614</v>
+      </c>
+      <c r="C42">
+        <v>19</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" t="s">
+        <v>134</v>
+      </c>
+      <c r="G42" t="s">
+        <v>135</v>
+      </c>
+      <c r="H42" t="s">
+        <v>136</v>
+      </c>
+      <c r="I42">
+        <v>1000</v>
+      </c>
+      <c r="J42" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43">
+        <v>685552</v>
+      </c>
+      <c r="C43">
+        <v>19</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>4711500240</v>
+      </c>
+      <c r="F43" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43" t="s">
+        <v>139</v>
+      </c>
+      <c r="H43" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43">
+        <v>1000</v>
+      </c>
+      <c r="J43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44">
+        <v>685552</v>
+      </c>
+      <c r="C44">
+        <v>19</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>4711500240</v>
+      </c>
+      <c r="F44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H44" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44">
+        <v>1000</v>
+      </c>
+      <c r="J44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45">
+        <v>685552</v>
+      </c>
+      <c r="C45">
+        <v>19</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>4711500240</v>
+      </c>
+      <c r="F45" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" t="s">
+        <v>139</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45">
+        <v>1000</v>
+      </c>
+      <c r="J45" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
